--- a/suppliers.xlsx
+++ b/suppliers.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Поставщики" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Поставщики'!$A$1:$V$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Поставщики'!$A$1:$V$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Одежда, Аксессуары</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Комбинезоны, куртки, попоны, жилеты, пыльники, охлаждающая коллекция; сумки для выгула и дождевик для владельца.</t>
+          <t>Мембранные комбинезоны, куртки и попоны, жилеты, пыльники, охлаждающая коллекция; сумки для выгула, сумочки для лакомств, диспенсер для пакетов, дождевик для владельца.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -624,12 +624,12 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Опт и минимальная партия — запросить. Пошив под заказ 5–7 рабочих дней.</t>
+          <t>Интересные позиции (розница в Украине): мембранный комбинезон 2 116–2 785 грн (29 размеров), мембранная попона 1 980 грн (24 размера), сумочка для лакомств 600–700 грн, диспенсер для пакетов 350 грн. Пошив под заказ 5–7 рабочих дней. Опт и минимальная партия — запросить.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>На сайте есть раздел «Співпраця», но без условий.</t>
+          <t>На сайте есть раздел «Співпраця», но без условий. Большая размерная сетка и пошив под заказ позволяют продавать по замерам без склада.</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -637,16 +637,16 @@
           <t>https://barkandgo.com.ua/</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
           <t>https://www.etsy.com/shop/BarkAndGo</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
           <t>info.barkandgo.ua@gmail.com</t>
@@ -679,7 +679,7 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Одежда</t>
@@ -712,12 +712,12 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Опт — через Suziria Brands, запросить. Розница: комбинезон для таксы около 620–960 грн.</t>
+          <t>Интересные позиции (розница в Украине): комбинезон COLD 564–593 грн, дождевик RAIN 553–640 грн, жилет E.Vest 541–649 грн, светоотражающий Yellow Vest 354 грн, комбинезон Milly с размерами под корги 1 215 грн. Размеры до 7XL. Опт — через Suziria Brands, запросить.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Крупный производитель: эксклюзив маловероятен. Польского дистрибьютора одежды поиск не нашёл.</t>
+          <t>Крупный производитель: эксклюзив маловероятен. Лекала под таксу при проверке сайта 12.10.2026 не подтверждены.</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -725,26 +725,26 @@
           <t>https://pet-fashion.com.ua/</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/petfashion_tm</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/petfashion.tm</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>https://www.youtube.com/channel/UCVrt1m3VlfDR0LVjD6ogkyA</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
       <c r="U3" s="3" t="inlineStr">
         <is>
           <t>https://mind.ua/news/20266537-ukrayinska-suziria-brands-vihodit-na-rinki-polshchi-ta-niderlandiv</t>
@@ -767,10 +767,10 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Одежда, Амуниция</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Опт и минимальная партия — запросить.</t>
+          <t>Интересные позиции (розница в Украине): дождевик для такс 545–745 грн, зимний комбинезон для такс 920 грн, дождевик со шлейкой 920 грн, дождевик для крупных собак 1 175 грн, поводок Hands Free 510 грн. Опт и дропшиппинг — через форму на сайте, условия запросить.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Дистрибьютора в ЕС поиск не нашёл.</t>
+          <t>Ткань дождевиков — водоотталкивающая плащёвка, не мембрана. Дистрибьютора в ЕС поиск не нашёл.</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -813,20 +813,20 @@
           <t>https://dogsbomba.com/</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/dogs_bomba</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="n"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
           <t>https://www.etsy.com/shop/DogsBomba</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="inlineStr">
         <is>
           <t>dogsbomba@gmail.com</t>
@@ -886,7 +886,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Куртки, дождевики, трикотаж, пледы; шьют с 2015 года.</t>
+          <t>Небольшое ателье: дождевики, лёгкие и тёплые куртки, жилеты, свитеры, бомберы; своя размерная сетка по породам, правка под размер.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Опт — запросить. Розница по статье 2021 года: 700–1 300 грн.</t>
+          <t>Интересные позиции (розница в Украине): дождевик 1 300–1 500 грн, тёплая куртка 1 800–2 100 грн. Опт — запросить.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Контакты на сайте не извлеклись, писать через Instagram.</t>
+          <t>Почта на сайте скрыта защитой, писать через Instagram. Объёмы ателье небольшие.</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -909,22 +909,22 @@
           <t>https://www.woofitdogwear.com/</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/woofitdogwear</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/woofitdogwear/</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="n"/>
       <c r="U5" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
@@ -992,19 +992,19 @@
           <t>Сайт montmorency.com.ua сейчас отдаёт 404 — проверить, работает ли бренд.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/montmorency_for_pets</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n"/>
       <c r="U6" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Одежда, Лежаки и дом</t>
+          <t>Одежда, Лежаки и дом, Аксессуары</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Запросить. Розница по статье 2021 года: одежда 330–640 грн, лежаки 400–2 000 грн.</t>
+          <t>Интересные позиции (розница в Украине): дождевик от 990 грн, комбинезон от 1 650 грн, сумка-коврик Travel 1 300 грн. Магазинам и салонам обещают спецусловия, фото и печатные материалы; есть каталог для скачивания.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Уже продаёт за рубеж в розницу через Etsy.</t>
+          <t>Уже продаёт за рубеж в розницу через Etsy. В подвале сайта стоит 2014–2022 — проверить, что бренд работает.</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -1077,12 +1077,12 @@
           <t>https://noblepet.com.ua/</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/noble_pet</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/noblepet.com.ua</t>
         </is>
@@ -1092,9 +1092,9 @@
           <t>https://www.etsy.com/shop/NoblePetStore</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
           <t>noblepetco@gmail.com</t>
@@ -1127,7 +1127,7 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Расходники</t>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Розница 100–170 грн за упаковку. Опт — запросить.</t>
+          <t>Интересные позиции (розница в Украине): «месячный запас» пакетов из кукурузного крахмала 130 грн, крахмальные пакеты 150–170 грн, контейнер для рулонов 80 грн. Опт — запросить.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Сертификат компостируемости на главной не назван — запросить документ.</t>
+          <t>Пакеты «БИО» — полиэтилен с добавкой-биодеградантом: проверить, не подпадают ли под запрет ЕС на оксоразлагаемый пластик, до проверки не брать. Сертификат компостируемости крахмальных пакетов на сайте не назван — запросить документ.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1173,24 +1173,24 @@
           <t>https://lavgav.ua/</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/welovegaw</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/welovegaw</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@welovegaw</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>https://www.youtube.com/channel/UC6nuUqtOEUtWTPOajtu6E-Q</t>
         </is>
@@ -1219,7 +1219,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>БроніК9</t>
+          <t>IPO4YOU</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Львов</t>
+          <t>Киев</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1254,56 +1254,48 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Амуниция для служебных собак: шлейки, тактические ошейники и поводки, намордники, обувь, защита.</t>
+          <t>Снаряжение для дрессировки и спорта с собакой: биотановые и паракордовые поводки, следовые поводки и шлейки, кожаные шлейки и ошейники, шлейка ASTA; одежда для кинологов, аджилити-инвентарь.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Вариант для крупных и рабочих собак и собачьего спорта.</t>
+          <t>Амуниция для дрессировки — то, что рекомендуют кинологи; команда сама ведёт занятия и семинары. Есть раздел индивидуального заказа.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Опт не указан. В Европу отправляют по индивидуальной договорённости, 7–14 рабочих дней.</t>
+          <t>Интересные позиции (розница в Украине): биотановый поводок с ручкой 452–1 267 грн, биотановый круглый поводок 498–1 674 грн, следовой поводок 10 м 1 357–1 448 грн, паракордовый поводок 163–362 грн, шлейка ASTA 1 403–1 629 грн, кожаная шлейка 1 674 грн. Опт — запросить.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>По сайту это магазин; уточнить, что шьют сами.</t>
+          <t>Что производят сами, а что перепродают — на сайте не указано, уточнить. Контактов на главной нет, писать через Instagram.</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>https://bronik9.com.ua/</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bronik_k9</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/BronikK9</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>https://youtube.com/@BroniK9</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>+380981789756</t>
-        </is>
-      </c>
+          <t>https://www.ipo4you.com.ua/</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ipo4you/</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/260988080909100/</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2" t="n"/>
+      <c r="T9" s="2" t="n"/>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>https://bronik9.com.ua</t>
+          <t>https://www.ipo4you.com.ua/</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1315,7 +1307,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Mr. Snoopy</t>
+          <t>BioIntellect</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1323,10 +1315,14 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Киев</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Амуниция, Одежда</t>
+          <t>Амуниция, Аксессуары</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1336,50 +1332,58 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Проверить</t>
+          <t>Шорт-лист</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Не найдено</t>
+          <t>Есть магазины-партнёры (Испания)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Ошейники, поводки, шлейки; худи, дождевики, зимние жилеты.</t>
+          <t>Амуниция из оригинального BioThane®: поводки 2–5 м (облегчённые для собак до 10 кг и классические), перестёжки «свободные руки», анатомические шлейки, ошейники; светоотражающие банданы, жёлтые маркеры настроения.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Один из немногих найденных украинских брендов именно амуниции.</t>
+          <t>Закрывает ядро ассортимента — поводки, шлейки, ошейники. Фурнитура из Чехии и Италии, отдельная облегчённая линейка для мелких собак. Сами зовут в опт и готовы брендировать амуницию логотипом партнёра.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Запросить. Цены 2021 года: поводок от 200 грн.</t>
+          <t>Интересные позиции (розница в Украине): поводок облегчённый 3 м для собак до 10 кг 1 265 грн, поводок классический 3 м 1 550 грн, перестёжка 1 620–2 333 грн, анатомическая шлейка 1 150–1 350 грн, ошейник 400–915 грн, бандана светоотражающая 255 грн. Опт: гибкие условия, коммерческое предложение по запросу.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Сайт mrsnoopy.com не открывается — проверить, работает ли бренд.</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/mrsnoopythedog</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
+          <t>По их словам, уже работают с магазинами в Украине, Израиле и Испании — эксклюзив в ЕС уточнить. Ширина ленты 9, 16 и 19 мм.</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>https://biointellect.net/</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>biointellectanimals@gmail.com</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>+380631079615</t>
+        </is>
+      </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
+          <t>https://biointellect.net/hurtova-spivpratsia-z-biointellect/</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1391,7 +1395,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Rebellious Collars</t>
+          <t>БроніК9</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1399,7 +1403,11 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Львов</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Амуниция</t>
@@ -1407,7 +1415,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Все размеры</t>
+          <t>Средние и крупные</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1422,36 +1430,56 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Мастерская: ошейники из натуральной кожи под размер и цвет.</t>
+          <t>Магазин амуниции для служебных собак: шлейки, тактические ошейники и поводки, намордники, обувь, защита. Большая часть — чужие бренды (OneTigris, Letsperfect, норвежская амуниция).</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Кожаная амуниция ручной работы.</t>
+          <t>Вариант для крупных и рабочих собак и собачьего спорта.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Неизвестно.</t>
+          <t>Похоже на своё производство (уточнить): шлейки К9 1 655 и 2 510 грн, комплект К9 ошейник с поводком 845 грн, амортизирующий поводок 440 грн. Опт не указан. В Европу отправляют по индивидуальной договорённости, 7–14 рабочих дней.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Контакты поиском не нашлись — искать в Instagram.</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr"/>
+          <t>Что шьют сами — по сайту не видно, вывод сделан по названиям товаров.</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>https://bronik9.com.ua/</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bronik_k9</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BronikK9</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@BroniK9</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>+380981789756</t>
+        </is>
+      </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>https://shotam.info/ukrains-ki-zootovary-top-10-vyrobnykiv-odiahu-budynochkiv-ta-smakolykiv-dlia-tvaryn/</t>
+          <t>https://bronik9.com.ua</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1463,7 +1491,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Best 4 Dogs</t>
+          <t>Mr. Snoopy</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1471,10 +1499,10 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Амуниция</t>
+          <t>Амуниция, Одежда</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1494,36 +1522,40 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Профессиональная амуниция: несколько видов поводков и ошейников.</t>
+          <t>Ошейники, поводки, шлейки; худи, дождевики, зимние жилеты.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Возможный источник поводков для дрессировки.</t>
+          <t>Один из немногих найденных украинских брендов именно амуниции.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Неизвестно.</t>
+          <t>Запросить. Цены 2021 года: поводок от 200 грн.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Сайт best4dogs.com.ua не открывается — проверить, работает ли бренд.</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr"/>
+          <t>Сайт mrsnoopy.com не открывается — проверить, работает ли бренд.</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mrsnoopythedog</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="n"/>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/best-4-dogs/</t>
+          <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1535,7 +1567,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Dogtag</t>
+          <t>Rebellious Collars</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1543,14 +1575,10 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Киев</t>
-        </is>
-      </c>
+      <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Адресники</t>
+          <t>Амуниция</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1570,44 +1598,36 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Адресники с гравировкой телефона владельца, разные формы и размеры.</t>
+          <t>Мастерская: ошейники из натуральной кожи под размер и цвет.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Недорогое персональное дополнение к заказу.</t>
+          <t>Кожаная амуниция ручной работы.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Запросить.</t>
+          <t>Неизвестно.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Город — предположение по домену.</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>http://dogtag.kiev.ua</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/dogtag.kiev.ua</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+          <t>Контакты поиском не нашлись — искать в Instagram.</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2" t="n"/>
+      <c r="T13" s="2" t="n"/>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/dogtag/</t>
+          <t>https://shotam.info/ukrains-ki-zootovary-top-10-vyrobnykiv-odiahu-budynochkiv-ta-smakolykiv-dlia-tvaryn/</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1619,7 +1639,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Vitameat</t>
+          <t>Best 4 Dogs</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1627,14 +1647,10 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Киев</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Лакомства</t>
+          <t>Амуниция</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1644,7 +1660,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Отложен</t>
+          <t>Проверить</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1654,68 +1670,36 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Сушёное мясо и субпродукты, один ингредиент в пачке, без добавок.</t>
+          <t>Профессиональная амуниция: несколько видов поводков и ошейников.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Сильный продукт для расходников.</t>
+          <t>Возможный источник поводков для дрессировки.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Запросить.</t>
+          <t>Неизвестно.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Ввоз кормов животного происхождения в ЕС требует ветеринарных разрешений — пока вне нашей схемы.</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>https://vitameat.com.ua/</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/vitameat.kyiv</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/Vitameat</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vitameat</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>https://t.me/vitameat</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@vitameat_kyiv</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>info@vitameat.com.ua</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>+380732839011</t>
-        </is>
-      </c>
+          <t>Сайт best4dogs.com.ua не открывается — проверить, работает ли бренд.</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n"/>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>https://vitameat.com.ua/</t>
+          <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/best-4-dogs/</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1727,7 +1711,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BASIC.FOOD</t>
+          <t>Dogtag</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1737,12 +1721,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Ровно</t>
+          <t>Киев</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Лакомства</t>
+          <t>Адресники</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1762,56 +1746,44 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Сушёные говяжьи субпродукты: лёгкие, сердце, печень, рубец.</t>
+          <t>Адресники с гравировкой телефона владельца, разные формы и размеры.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Простой состав без консервантов.</t>
+          <t>Недорогое персональное дополнение к заказу.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Запросить.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
+          <t>На сайте одна строка: мастерская закрыта, ушли в ВСУ (проверено 12.10.2026).</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>https://basic-food.shop/</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/basic.rivne</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>https://t.me/basic_food_bot</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>info@basic-food.shop</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>+380976655442</t>
-        </is>
-      </c>
+          <t>http://dogtag.kiev.ua</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dogtag.kiev.ua</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="n"/>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>https://basic-food.shop/</t>
+          <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/dogtag/</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -1823,7 +1795,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Ласощі з села</t>
+          <t>Vitameat</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1833,7 +1805,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Запорожье</t>
+          <t>Киев</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1858,12 +1830,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Сушёные говяжьи субпродукты широкой линейкой; производитель — ТД «Едельвейс Україна».</t>
+          <t>Сушёное мясо и субпродукты, один ингредиент в пачке, без добавок.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Работают оптом, большой ассортимент.</t>
+          <t>Сильный продукт для расходников.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1873,37 +1845,53 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
+          <t>Ввоз кормов животного происхождения в ЕС требует ветеринарных разрешений — пока вне нашей схемы.</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://www.lasoshizsela.com/</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/lasochi_z_sela</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1171886699563323</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+          <t>https://vitameat.com.ua/</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vitameat.kyiv</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vitameat</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@vitameat</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/vitameat</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@vitameat_kyiv</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>korma.zp.ua@gmail.com</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr"/>
+          <t>info@vitameat.com.ua</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>+380732839011</t>
+        </is>
+      </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>https://www.lasoshizsela.com/</t>
+          <t>https://vitameat.com.ua/</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -1915,7 +1903,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SNACK'ON</t>
+          <t>BASIC.FOOD</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1923,7 +1911,11 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Ровно</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Лакомства</t>
@@ -1946,12 +1938,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Крафтовые сушёные лакомства из говядины.</t>
+          <t>Сушёные говяжьи субпродукты: лёгкие, сердце, печень, рубец.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Небольшое производство, без консервантов.</t>
+          <t>Простой состав без консервантов.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1961,25 +1953,41 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>То же ограничение: ветеринарные разрешения на ввоз. Сайт открывается с ошибкой сертификата.</t>
+          <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>https://snackon.com.ua/</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr"/>
+          <t>https://basic-food.shop/</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/basic.rivne</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/basic_food_bot</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>info@basic-food.shop</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>+380976655442</t>
+        </is>
+      </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>https://snackon.com.ua/</t>
+          <t>https://basic-food.shop/</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -1991,7 +1999,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Harley&amp;Cho</t>
+          <t>Ласощі з села</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1999,10 +2007,14 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Запорожье</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Лежаки и дом</t>
+          <t>Лакомства</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2017,69 +2029,57 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Уже в ЕС</t>
+          <t>Не найдено</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Лежаки, диваны, миски на подставке, автогамаки; немного амуниции.</t>
+          <t>Сушёные говяжьи субпродукты широкой линейкой; производитель — ТД «Едельвейс Україна».</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Известный бренд, но не наша стартовая категория.</t>
+          <t>Работают оптом, большой ассортимент.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Запросить.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Похоже, уже есть немецкий сайт — уникальности не будет.</t>
+          <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>https://harleyandcho.ua/</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/harleyandcho</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/harleyandcho.main</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.etsy.com/listing/584236455</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@HarleyandCho</t>
-        </is>
-      </c>
+          <t>https://www.lasoshizsela.com/</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lasochi_z_sela</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1171886699563323</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>info@harleyandcho.ua</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>+380674527445</t>
-        </is>
-      </c>
+          <t>korma.zp.ua@gmail.com</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="n"/>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>https://harleyandcho.ua/</t>
+          <t>https://www.lasoshizsela.com/</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Collar / WAUDOG</t>
+          <t>SNACK'ON</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2099,14 +2099,10 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Чернигов</t>
-        </is>
-      </c>
+      <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Амуниция, Одежда</t>
+          <t>Лакомства</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2121,45 +2117,45 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Уже в ЕС</t>
+          <t>Не найдено</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Ошейники, поводки, шлейки, адресники с QR, куртки AiryVest, Puller.</t>
+          <t>Крафтовые сушёные лакомства из говядины.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Ориентир по качеству, а не поставщик для уникального ассортимента.</t>
+          <t>Небольшое производство, без консервантов.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Опт в Польше — через COLLAR PL.</t>
+          <t>Запросить.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Продаётся в 70 странах, в Польше есть своя компания.</t>
+          <t>То же ограничение: ветеринарные разрешения на ввоз. Сайт открывается с ошибкой сертификата.</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>https://collar.com/</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr"/>
+          <t>https://snackon.com.ua/</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n"/>
+      <c r="S19" s="2" t="n"/>
+      <c r="T19" s="2" t="n"/>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>https://forbes.ua/company/eksperimenty-na-zhivotnykh-17022021-1037</t>
+          <t>https://snackon.com.ua/</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2171,7 +2167,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Bronzedog</t>
+          <t>Harley&amp;Cho</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2179,10 +2175,10 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Амуниция, Одежда</t>
+          <t>Лежаки и дом</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2197,17 +2193,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Не найдено</t>
+          <t>Уже в ЕС</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Ошейники, шлейки, поводки, намордники, одежда.</t>
+          <t>Лежаки, диваны, миски на подставке, автогамаки; немного амуниции.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Широкая линейка амуниции.</t>
+          <t>Известный бренд, но не наша стартовая категория.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2217,21 +2213,49 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Часть товара сделана в Китае — не «украинское производство».</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr"/>
+          <t>Похоже, уже есть немецкий сайт — уникальности не будет.</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>https://harleyandcho.ua/</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/harleyandcho</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/harleyandcho.main</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/listing/584236455</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@HarleyandCho</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>info@harleyandcho.ua</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>+380674527445</t>
+        </is>
+      </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>https://e-zoo.com.ua/ua/139-amuniciya-dlya-sobak/f/12956-biotan</t>
+          <t>https://harleyandcho.ua/</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2243,71 +2267,75 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DIQPET</t>
+          <t>Collar / WAUDOG</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Китай</t>
+          <t>Украина</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Шанхай</t>
+          <t>Чернигов</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Амуниция, Одежда</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Мелкие (до 8 кг)</t>
+          <t>Все размеры</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>В переписке</t>
+          <t>Отложен</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Не применимо</t>
+          <t>Уже в ЕС</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Urban Trekking Onesie: комбинезон на четыре лапы со встроенными ботинками. Есть отдельная линия на собак до 40 кг.</t>
+          <t>Ошейники, поводки, шлейки, адресники с QR, куртки AiryVest, Puller.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Функциональная вещь для грязи и мокрого снега; поставщик честно описывает ограничения ткани.</t>
+          <t>Ориентир по качеству, а не поставщик для уникального ассортимента.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>MOQ 30 шт., размеры можно смешивать, один цвет. Образцы: 2 шт. Прайс и доставка — в ответе от 07.10.2026.</t>
+          <t>Опт в Польше — через COLLAR PL.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Крой корейский: размеры меньше европейских, подбирать по обхвату груди. Ткань водоотталкивающая, не мембрана.</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr"/>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>Ответ DIQPET на 11 вопросов, 07.10.2026 (файл у команды)</t>
+          <t>Продаётся в 70 странах, в Польше есть своя компания.</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>https://collar.com/</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
+      <c r="T21" s="2" t="n"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>https://forbes.ua/company/eksperimenty-na-zhivotnykh-17022021-1037</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2319,145 +2347,278 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>Bronzedog</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Украина</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Амуниция, Одежда</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Все размеры</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Отложен</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Не найдено</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Ошейники, шлейки, поводки, намордники, одежда.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Широкая линейка амуниции.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Часть товара сделана в Китае — не «украинское производство».</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>https://e-zoo.com.ua/ua/139-amuniciya-dlya-sobak/f/12956-biotan</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>DIQPET</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Китай</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Шанхай</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Мелкие (до 8 кг)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>В переписке</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Urban Trekking Onesie: комбинезон на четыре лапы со встроенными ботинками. Есть отдельная линия на собак до 40 кг.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Функциональная вещь для грязи и мокрого снега; поставщик честно описывает ограничения ткани.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>MOQ 30 шт., размеры можно смешивать, один цвет. Образцы: 2 шт. Прайс и доставка — в ответе от 07.10.2026.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Крой корейский: размеры меньше европейских, подбирать по обхвату груди. Ткань водоотталкивающая, не мембрана.</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="n"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>Ответ DIQPET на 11 вопросов, 07.10.2026 (файл у команды)</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Merlot Studio</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Корея</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Одежда</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Все размеры</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>В переписке</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Не применимо</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Одежда для собак: Coore Top / Suit, Ain Coat / Suit; размеры S–5XL, до 50 кг.</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Корейский ассортимент не только на мелких собак — редкость.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Каталог 25SS получен. MOQ и прайс дистрибьютора — запросить.</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Контакт — в переписке у команды.</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr"/>
-      <c r="T22" s="2" t="inlineStr"/>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="3" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="3" t="inlineStr">
         <is>
           <t>Каталог Merlot 25SS (файл у команды)</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>12.10.2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V22"/>
+  <autoFilter ref="A1:V24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/suppliers.xlsx
+++ b/suppliers.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Поставщики" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Поставщики'!$A$1:$V$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Поставщики'!$A$1:$AA$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -445,23 +445,28 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
     <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="32" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="28" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,85 +497,110 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Приоритет</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Переговоры</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ценовой сегмент</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Присутствие в ЕС</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Оценка команды</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Следующий шаг</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Что делает</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Почему нам</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Из поиска</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Условия и цены</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Заметка</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Каталог</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Etsy</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Telegram</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Проверено</t>
         </is>
@@ -579,7 +609,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bark&amp;Go</t>
+          <t>Noble Pet</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -589,12 +619,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Львов</t>
+          <t>Харьков</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Одежда, Лежаки и дом</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -604,74 +634,103 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Шорт-лист</t>
+          <t>Первая очередь</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>Только розница (Etsy)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Комбинезоны, куртки, попоны, жилеты, пыльники, охлаждающая коллекция; сумки для выгула и дождевик для владельца.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Около 10 лет на рынке. По подкасту SendPulse (июнь 2026) основательница выбирает дистрибьюторов и фокусные рынки — партнёра ищут сами.</t>
-        </is>
-      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Опт и минимальная партия — запросить. Пошив под заказ 5–7 рабочих дней.</t>
+          <t>Понравились модели и описание товаров.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>На сайте есть раздел «Співпраця», но без условий.</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>https://barkandgo.com.ua/</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.etsy.com/shop/BarkAndGo</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>info.barkandgo.ua@gmail.com</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>+380677494005</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://sendpulse.ua/blog/podkast-z-oleksandroiu-vakarovoiu</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+          <t>Изучить подробнее. Проверить размерную сетку, посадку, качество и оптовые условия.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Одежда, лежаки и подушки, автогамаки для перевозки собак.</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Широкая линейка у одного производителя, невысокие цены.</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Запросить. Розница по статье 2021 года: одежда 330–640 грн, лежаки 400–2 000 грн.</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Уже продаёт за рубеж в розницу через Etsy.</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>https://noblepet.com.ua/</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>https://noblepet.com.ua/yak-zrobyty-zamiry/</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/noble_pet</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/noblepet.com.ua</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/shop/NoblePetStore</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>noblepetco@gmail.com</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>+380667836190</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Pet Fashion</t>
+          <t>BioIntellect</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -679,10 +738,14 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Киев</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Амуниция</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -692,74 +755,91 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Шорт-лист</t>
+          <t>Первая очередь</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Комбинезоны, дождевики, жилеты, худи; отдельные лекала под таксу и другие породы.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Попадает в нишу такс. У владельца (Suziria Group) уже есть канал в Польшу для корма Savory через Hovet.</t>
-        </is>
-      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Опт — через Suziria Brands, запросить. Розница: комбинезон для таксы около 620–960 грн.</t>
+          <t>Амуниция выглядит отлично. Уже был положительный опыт с амуницией из этого же биотана: прослужила около 5 лет. Весь ассортимент выглядит перспективно.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Крупный производитель: эксклюзив маловероятен. Польского дистрибьютора одежды поиск не нашёл.</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>https://pet-fashion.com.ua/</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/petfashion_tm</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/petfashion.tm</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCVrt1m3VlfDR0LVjD6ogkyA</t>
-        </is>
-      </c>
+          <t>Изучить полный каталог, оптовые цены и возможность перепродажи в Польше.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Амуниция из биотана: перестёжки «свободные руки», поводки до и от 10 кг, анатомические шлейки, ошейники; ремонт поводков.</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Свой производитель биотановой амуниции — закрывает наше ядро: шлейки и поводки.</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Розница: перестёжка 1 620–2 333 грн. Опт — запросить по почте: раздел «Співпраця» приглашает к предложениям.</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>В соцсетях — @BioIntellectUA.</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>https://biointellect.net/</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>https://biointellect.net/perestibky/</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://mind.ua/news/20266537-ukrayinska-suziria-brands-vihodit-na-rinki-polshchi-ta-niderlandiv</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>biointellectanimals@gmail.com</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>+380631079615</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>https://biointellect.net/spivpratsya/</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Dogs Bomba</t>
+          <t>IPO4YOU</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -767,91 +847,120 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Киев</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Амуниция, Игрушки и тренировка</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Все размеры</t>
+          <t>Средние и крупные</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Шорт-лист</t>
+          <t>Первая очередь</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Только розница (Etsy)</t>
+          <t>Не начаты</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Одежда с 2014 года, своя команда дизайнеров и швей; отдельные линейки для такс и корги.</t>
+          <t>Профессиональный</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Доступная цена и породные лекала: дождевик-комбинезон для таксы около 680–920 грн в рознице.</t>
+          <t>Не найдено</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Опт и минимальная партия — запросить.</t>
+          <t>Магазин профессиональной амуниции. Много полезных игрушек для тренировок и крупных собак.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Дистрибьютора в ЕС поиск не нашёл.</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>https://dogsbomba.com/</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dogs_bomba</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.etsy.com/shop/DogsBomba</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>dogsbomba@gmail.com</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>+380996891029</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://dogsbomba.com/</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+          <t>Рассмотреть для профессионального ассортимента. Изучить игрушки, тренировочный инвентарь и условия закупки.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Снаряжение для дрессировки: биотановые поводки и ошейники, шлейки, намордники, рукава и ухватки, инвентарь для следовой работы; одежда для кинологов.</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Профессиональный ассортимент для собачьего спорта; есть индивидуальный заказ.</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Опт — запросить. На сайте указано: работают по Украине и Европе.</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Проводят семинары и занятия в Киеве — близки нам по духу. Что шьют сами, а что перепродают — уточнить.</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ipo4you.com.ua/ua/</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ipo4you.com.ua/ua/shop/</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ipo4you</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/260988080909100</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCUZNYkwFYAoHf4dlhgjNi-Q</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>+380677062274</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ipo4you.com.ua/ua/</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Woofit</t>
+          <t>Bark&amp;Go</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -861,7 +970,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Киев</t>
+          <t>Львов</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -876,70 +985,95 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Проверить</t>
+          <t>Вторая очередь</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Не найдено</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Куртки, дождевики, трикотаж, пледы; шьют с 2015 года.</t>
-        </is>
-      </c>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Начинали с пошива по индивидуальным меркам — можно обсуждать нестандартные размеры.</t>
+          <t>Только розница (Etsy)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Опт — запросить. Розница по статье 2021 года: 700–1 300 грн.</t>
+          <t>Есть интересные модели дождевиков и другой одежды, но дизайн многих моделей слишком пёстрый и обычный. Можно собирать парные луки «человек + собака».</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Контакты на сайте не извлеклись, писать через Instagram.</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.woofitdogwear.com/</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/woofitdogwear</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/woofitdogwear/</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Изучить подробнее. Проверить модели для парных образов и потенциал продажи в Польше.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Комбинезоны, куртки, попоны, жилеты, пыльники, охлаждающая коллекция; сумки для выгула и дождевик для владельца.</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Около 10 лет на рынке. По подкасту SendPulse (июнь 2026) основательница выбирает дистрибьюторов и фокусные рынки — партнёра ищут сами.</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Опт и минимальная партия — запросить. Пошив под заказ 5–7 рабочих дней.</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>На сайте есть раздел «Співпраця», но без условий.</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>https://barkandgo.com.ua/</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>https://barkandgo.com.ua/shop/sobaka/doschoviki-legki/</t>
+        </is>
+      </c>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/shop/BarkAndGo</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>info.barkandgo.ua@gmail.com</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>+380677494005</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>https://sendpulse.ua/blog/podkast-z-oleksandroiu-vakarovoiu</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Montmorency</t>
+          <t>Dogs Bomba</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -947,11 +1081,7 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Киев</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Одежда</t>
@@ -964,62 +1094,103 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Проверить</t>
+          <t>Вторая очередь</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Не найдено</t>
+          <t>Не начаты</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Одежда и аксессуары для собак и кошек, своё ателье, пошив по меркам.</t>
+          <t>Бюджетный</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Премиальный сегмент: 1 500–3 000 грн за вещь (цены 2021 года).</t>
+          <t>Только розница (Etsy)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Запросить.</t>
+          <t>Ничего необычного или уникального, но есть интересные модели для дешёвого сегмента. Есть товары для такс.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Сайт montmorency.com.ua сейчас отдаёт 404 — проверить, работает ли бренд.</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/montmorency_for_pets</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+          <t>Рассмотреть бюджетный сегмент. Отдельно изучить ассортимент для такс.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Одежда с 2014 года, своя команда дизайнеров и швей; отдельные линейки для такс и корги.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Доступная цена и породные лекала: дождевик-комбинезон для таксы около 680–920 грн в рознице.</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Опт и минимальная партия — запросить.</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Дистрибьютора в ЕС поиск не нашёл.</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>https://dogsbomba.com/</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://dogsbomba.com/catalog/platya/</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dogs_bomba</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/shop/DogsBomba</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>dogsbomba@gmail.com</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>+380996891029</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>https://dogsbomba.com/</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Noble Pet</t>
+          <t>Woofit</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1029,12 +1200,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Харьков</t>
+          <t>Киев</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Одежда, Лежаки и дом</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1044,75 +1215,88 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Проверить</t>
+          <t>Вторая очередь</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Только розница (Etsy)</t>
+          <t>Не начаты</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Одежда, лежаки и подушки, автогамаки для перевозки собак.</t>
+          <t>Бюджетный</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Широкая линейка у одного производителя, невысокие цены.</t>
+          <t>Не найдено</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Запросить. Розница по статье 2021 года: одежда 330–640 грн, лежаки 400–2 000 грн.</t>
+          <t>Есть неплохие модели, но они тоже ориентированы на дешёвый сегмент.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Уже продаёт за рубеж в розницу через Etsy.</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>https://noblepet.com.ua/</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/noble_pet</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/noblepet.com.ua</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.etsy.com/shop/NoblePetStore</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>noblepetco@gmail.com</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>+380667836190</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
+          <t>Сравнить цены и качество. Рассматривать для бюджетной линейки.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Куртки, дождевики, трикотаж, пледы; шьют с 2015 года.</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Начинали с пошива по индивидуальным меркам — можно обсуждать нестандартные размеры.</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Опт — запросить. Розница по статье 2021 года: 700–1 300 грн.</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Контакты на сайте не извлеклись, писать через Instagram.</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.woofitdogwear.com/</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.woofitdogwear.com/product-category/raincoats/</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woofitdogwear</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/woofitdogwear/</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
@@ -1140,86 +1324,107 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Шорт-лист</t>
+          <t>Вторая очередь</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Только пакеты для уборки за собаками, но выглядят плотными.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Проверить качество, толщину, стоимость упаковки и цену за один пакет.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Пакеты для уборки: из кукурузного крахмала (домашнее компостирование) и обычные; контейнер для рулонов.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Есть готовый «месячный запас» — наша механика расходников. Приглашают зоомагазины и салоны в партнёры.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Розница 100–170 грн за упаковку. Опт — запросить.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Сертификат компостируемости на главной не назван — запросить документ.</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>https://lavgav.ua/</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://lavgav.ua/faq</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/welovegaw</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/welovegaw</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@welovegaw</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/channel/UC6nuUqtOEUtWTPOajtu6E-Q</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>welovegaw@gmail.com</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>+380639351463</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>https://lavgav.ua/</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>БроніК9</t>
+          <t>Vitameat</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1229,93 +1434,126 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Львов</t>
+          <t>Киев</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Амуниция</t>
+          <t>Лакомства</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Средние и крупные</t>
+          <t>Все размеры</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Проверить</t>
+          <t>Вторая очередь</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Амуниция для служебных собак: шлейки, тактические ошейники и поводки, намордники, обувь, защита.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Вариант для крупных и рабочих собак и собачьего спорта.</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Опт не указан. В Европу отправляют по индивидуальной договорённости, 7–14 рабочих дней.</t>
+          <t>Хорошие лакомства, но есть сомнения, будет ли цена конкурентоспособной в Польше.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>По сайту это магазин; уточнить, что шьют сами.</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>https://bronik9.com.ua/</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bronik_k9</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/BronikK9</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>Сравнить стоимость с польскими аналогами с учётом доставки и наценки.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Сушёное мясо и субпродукты, один ингредиент в пачке, без добавок.</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Сильный продукт для расходников.</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Запросить.</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Ввоз кормов животного происхождения в ЕС требует ветеринарных разрешений — пока вне нашей схемы.</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>https://vitameat.com.ua/</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://vitameat.com.ua/product-category/susheni-kovbaski/</t>
+        </is>
+      </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>https://youtube.com/@BroniK9</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>+380981789756</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/vitameat.kyiv</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vitameat</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>https://bronik9.com.ua</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+          <t>https://www.tiktok.com/@vitameat</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/vitameat</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@vitameat_kyiv</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>info@vitameat.com.ua</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>+380732839011</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>https://vitameat.com.ua/</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Mr. Snoopy</t>
+          <t>BASIC.FOOD</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1323,10 +1561,14 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Ровно</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Амуниция, Одежда</t>
+          <t>Лакомства</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1336,62 +1578,95 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Проверить</t>
+          <t>Вторая очередь</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Ошейники, поводки, шлейки; худи, дождевики, зимние жилеты.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Один из немногих найденных украинских брендов именно амуниции.</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Запросить. Цены 2021 года: поводок от 200 грн.</t>
+          <t>Аналогично VitaMeat: хорошие лакомства, но нужно сравнить цены с польским рынком.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Сайт mrsnoopy.com не открывается — проверить, работает ли бренд.</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/mrsnoopythedog</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
+          <t>Проверить себестоимость, составы, сроки годности и оптовые условия.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Сушёные говяжьи субпродукты: лёгкие, сердце, печень, рубец.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Простой состав без консервантов.</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Запросить.</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>https://basic-food.shop/</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/basic.rivne</t>
+        </is>
+      </c>
       <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/basic_food_bot</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>info@basic-food.shop</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>+380976655442</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>https://basic-food.shop/</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Rebellious Collars</t>
+          <t>Pet Fashion</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1402,7 +1677,7 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Амуниция</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1412,58 +1687,95 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Проверить</t>
+          <t>Третья очередь</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Мастерская: ошейники из натуральной кожи под размер и цвет.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Кожаная амуниция ручной работы.</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Неизвестно.</t>
+          <t>Совершенно обычная одежда. Ничем не отличается от польского рынка.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Контакты поиском не нашлись — искать в Instagram.</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
+          <t>Искать только товары с конкурентной ценой или интересными условиями опта.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Комбинезоны, дождевики, жилеты, худи; отдельные лекала под таксу и другие породы.</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Попадает в нишу такс. У владельца (Suziria Group) уже есть канал в Польшу для корма Savory через Hovet.</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Опт — через Suziria Brands, запросить. Розница: комбинезон для таксы около 620–960 грн.</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Крупный производитель: эксклюзив маловероятен. Польского дистрибьютора одежды поиск не нашёл.</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>https://pet-fashion.com.ua/</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://pet-fashion.com.ua/uk/60-dosshoviki-ta-vitrovki</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/petfashion_tm</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/petfashion.tm</t>
+        </is>
+      </c>
       <c r="T11" s="2" t="inlineStr"/>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://shotam.info/ukrains-ki-zootovary-top-10-vyrobnykiv-odiahu-budynochkiv-ta-smakolykiv-dlia-tvaryn/</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCVrt1m3VlfDR0LVjD6ogkyA</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>https://mind.ua/news/20266537-ukrayinska-suziria-brands-vihodit-na-rinki-polshchi-ta-niderlandiv</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Best 4 Dogs</t>
+          <t>Montmorency</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1471,10 +1783,14 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Киев</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Амуниция</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1484,58 +1800,83 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Проверить</t>
+          <t>Третья очередь</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Премиум</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Профессиональная амуниция: несколько видов поводков и ошейников.</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Возможный источник поводков для дрессировки.</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Неизвестно.</t>
+          <t>С 2023 года нет информации.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Сайт best4dogs.com.ua не открывается — проверить, работает ли бренд.</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
+          <t>Проверить, работает ли бренд сейчас и актуальны ли контакты.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Одежда и аксессуары для собак и кошек, своё ателье, пошив по меркам.</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Премиальный сегмент: 1 500–3 000 грн за вещь (цены 2021 года).</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Запросить.</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Сайт montmorency.com.ua сейчас отдаёт 404 — проверить, работает ли бренд.</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/montmorency_for_pets</t>
+        </is>
+      </c>
       <c r="S12" s="2" t="inlineStr"/>
       <c r="T12" s="2" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/best-4-dogs/</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Dogtag</t>
+          <t>БроніК9</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1545,81 +1886,118 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Киев</t>
+          <t>Львов</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Адресники</t>
+          <t>Амуниция</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Все размеры</t>
+          <t>Средние и крупные</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Проверить</t>
+          <t>Третья очередь</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Профессиональный</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Адресники с гравировкой телефона владельца, разные формы и размеры.</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Недорогое персональное дополнение к заказу.</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Запросить.</t>
+          <t>Слишком серьёзная амуниция. Больше подходит профессиональным спортсменам и служебным собакам.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Город — предположение по домену.</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>http://dogtag.kiev.ua</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/dogtag.kiev.ua</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
+          <t>Узкая профессиональная ниша, не для основного ассортимента.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Амуниция для служебных собак: шлейки, тактические ошейники и поводки, намордники, обувь, защита.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Вариант для крупных и рабочих собак и собачьего спорта.</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Опт не указан. В Европу отправляют по индивидуальной договорённости, 7–14 рабочих дней.</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>По сайту это магазин; уточнить, что шьют сами.</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>https://bronik9.com.ua/</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://bronik9.com.ua/category/5268-nashijniki-ta-povodki</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bronik_k9</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BronikK9</t>
+        </is>
+      </c>
       <c r="T13" s="2" t="inlineStr"/>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/dogtag/</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@BroniK9</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>+380981789756</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>https://bronik9.com.ua</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Vitameat</t>
+          <t>Best 4 Dogs</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1627,14 +2005,10 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Киев</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Лакомства</t>
+          <t>Амуниция</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1644,90 +2018,75 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Отложен</t>
+          <t>Третья очередь</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Сушёное мясо и субпродукты, один ингредиент в пачке, без добавок.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Сильный продукт для расходников.</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Запросить.</t>
+          <t>Ассортимент не понравился.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Ввоз кормов животного происхождения в ЕС требует ветеринарных разрешений — пока вне нашей схемы.</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>https://vitameat.com.ua/</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/vitameat.kyiv</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/Vitameat</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@vitameat</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>https://t.me/vitameat</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@vitameat_kyiv</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>info@vitameat.com.ua</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>+380732839011</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://vitameat.com.ua/</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+          <t>Низкий приоритет.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Профессиональная амуниция: несколько видов поводков и ошейников.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Возможный источник поводков для дрессировки.</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Неизвестно.</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Сайт best4dogs.com.ua не открывается; команда смотрела страницу в каталоге Made in UA.</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/best-4-dogs/</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BASIC.FOOD</t>
+          <t>Mr. Snoopy</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1735,14 +2094,10 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Ровно</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Лакомства</t>
+          <t>Амуниция, Одежда</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1752,78 +2107,71 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Отложен</t>
+          <t>Без приоритета</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Сушёные говяжьи субпродукты: лёгкие, сердце, печень, рубец.</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Простой состав без консервантов.</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Запросить.</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>https://basic-food.shop/</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/basic.rivne</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Ошейники, поводки, шлейки; худи, дождевики, зимние жилеты.</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Один из немногих найденных украинских брендов именно амуниции.</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Запросить. Цены 2021 года: поводок от 200 грн.</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Сайт mrsnoopy.com не открывается — проверить, работает ли бренд.</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>https://t.me/basic_food_bot</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>info@basic-food.shop</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>+380976655442</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>https://basic-food.shop/</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mrsnoopythedog</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr"/>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Ласощі з села</t>
+          <t>Rebellious Collars</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1831,14 +2179,10 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Запорожье</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Лакомства</t>
+          <t>Амуниция</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1848,74 +2192,67 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Отложен</t>
+          <t>Без приоритета</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Сушёные говяжьи субпродукты широкой линейкой; производитель — ТД «Едельвейс Україна».</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Работают оптом, большой ассортимент.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Запросить.</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.lasoshizsela.com/</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/lasochi_z_sela</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/1171886699563323</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Мастерская: ошейники из натуральной кожи под размер и цвет.</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Кожаная амуниция ручной работы.</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Неизвестно.</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Контакты поиском не нашлись — искать в Instagram.</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>korma.zp.ua@gmail.com</t>
-        </is>
-      </c>
+      <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.lasoshizsela.com/</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr"/>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>https://shotam.info/ukrains-ki-zootovary-top-10-vyrobnykiv-odiahu-budynochkiv-ta-smakolykiv-dlia-tvaryn/</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SNACK'ON</t>
+          <t>Dogtag</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1923,10 +2260,14 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Киев</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Лакомства</t>
+          <t>Адресники</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1936,62 +2277,75 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Отложен</t>
+          <t>Без приоритета</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>Не найдено</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Крафтовые сушёные лакомства из говядины.</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Небольшое производство, без консервантов.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Адресники с гравировкой телефона владельца, разные формы и размеры.</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Недорогое персональное дополнение к заказу.</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>То же ограничение: ветеринарные разрешения на ввоз. Сайт открывается с ошибкой сертификата.</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>https://snackon.com.ua/</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Город — предположение по домену.</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>http://dogtag.kiev.ua</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr"/>
       <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dogtag.kiev.ua</t>
+        </is>
+      </c>
       <c r="T17" s="2" t="inlineStr"/>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>https://snackon.com.ua/</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/dogtag/</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Harley&amp;Cho</t>
+          <t>Ласощі з села</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1999,10 +2353,14 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Запорожье</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Лежаки и дом</t>
+          <t>Лакомства</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2012,86 +2370,83 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Отложен</t>
+          <t>Без приоритета</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Уже в ЕС</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Лежаки, диваны, миски на подставке, автогамаки; немного амуниции.</t>
-        </is>
-      </c>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Известный бренд, но не наша стартовая категория.</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Похоже, уже есть немецкий сайт — уникальности не будет.</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>https://harleyandcho.ua/</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/harleyandcho</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/harleyandcho.main</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.etsy.com/listing/584236455</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
+          <t>Не найдено</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Сушёные говяжьи субпродукты широкой линейкой; производитель — ТД «Едельвейс Україна».</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Работают оптом, большой ассортимент.</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Запросить.</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lasoshizsela.com/</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@HarleyandCho</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>info@harleyandcho.ua</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>+380674527445</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>https://harleyandcho.ua/</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+          <t>https://www.instagram.com/lasochi_z_sela</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1171886699563323</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>korma.zp.ua@gmail.com</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lasoshizsela.com/</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Collar / WAUDOG</t>
+          <t>SNACK'ON</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2099,14 +2454,10 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Чернигов</t>
-        </is>
-      </c>
+      <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Амуниция, Одежда</t>
+          <t>Лакомства</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2116,62 +2467,71 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Отложен</t>
+          <t>Без приоритета</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Уже в ЕС</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Ошейники, поводки, шлейки, адресники с QR, куртки AiryVest, Puller.</t>
-        </is>
-      </c>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Ориентир по качеству, а не поставщик для уникального ассортимента.</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Опт в Польше — через COLLAR PL.</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Продаётся в 70 странах, в Польше есть своя компания.</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>https://collar.com/</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
+          <t>Не найдено</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Крафтовые сушёные лакомства из говядины.</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Небольшое производство, без консервантов.</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Запросить.</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>То же ограничение: ветеринарные разрешения на ввоз. Сайт открывается с ошибкой сертификата.</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>https://snackon.com.ua/</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="inlineStr"/>
       <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr"/>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t>https://forbes.ua/company/eksperimenty-na-zhivotnykh-17022021-1037</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr"/>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>https://snackon.com.ua/</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Bronzedog</t>
+          <t>Harley&amp;Cho</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2182,7 +2542,7 @@
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Амуниция, Одежда</t>
+          <t>Лежаки и дом</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2192,145 +2552,203 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Отложен</t>
+          <t>Без приоритета</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Не найдено</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Ошейники, шлейки, поводки, намордники, одежда.</t>
-        </is>
-      </c>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Широкая линейка амуниции.</t>
+          <t>Уже в ЕС</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>Для разнообразия можно заказывать.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Рассмотреть как дополнительного поставщика для расширения ассортимента.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Лежаки, диваны, миски на подставке, автогамаки; немного амуниции.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Известный бренд, но не наша стартовая категория.</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Часть товара сделана в Китае — не «украинское производство».</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Похоже, уже есть немецкий сайт — уникальности не будет.</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>https://harleyandcho.ua/</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr"/>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t>https://e-zoo.com.ua/ua/139-amuniciya-dlya-sobak/f/12956-biotan</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/harleyandcho</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/harleyandcho.main</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/listing/584236455</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@HarleyandCho</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>info@harleyandcho.ua</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>+380674527445</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>https://harleyandcho.ua/</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DIQPET</t>
+          <t>Collar / WAUDOG</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Китай</t>
+          <t>Украина</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Шанхай</t>
+          <t>Чернигов</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Амуниция, Одежда</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Мелкие (до 8 кг)</t>
+          <t>Все размеры</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>В переписке</t>
+          <t>Без приоритета</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Urban Trekking Onesie: комбинезон на четыре лапы со встроенными ботинками. Есть отдельная линия на собак до 40 кг.</t>
-        </is>
-      </c>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Функциональная вещь для грязи и мокрого снега; поставщик честно описывает ограничения ткани.</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>MOQ 30 шт., размеры можно смешивать, один цвет. Образцы: 2 шт. Прайс и доставка — в ответе от 07.10.2026.</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Крой корейский: размеры меньше европейских, подбирать по обхвату груди. Ткань водоотталкивающая, не мембрана.</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
+          <t>Уже в ЕС</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Ошейники, поводки, шлейки, адресники с QR, куртки AiryVest, Puller.</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Ориентир по качеству, а не поставщик для уникального ассортимента.</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Опт в Польше — через COLLAR PL.</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Продаётся в 70 странах, в Польше есть своя компания.</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>https://collar.com/</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr"/>
       <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr"/>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>Ответ DIQPET на 11 вопросов, 07.10.2026 (файл у команды)</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr"/>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>https://forbes.ua/company/eksperimenty-na-zhivotnykh-17022021-1037</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Merlot Studio</t>
+          <t>Bronzedog</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Корея</t>
+          <t>Украина</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Одежда</t>
+          <t>Амуниция, Одежда</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2340,124 +2758,316 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>В переписке</t>
+          <t>Без приоритета</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Одежда для собак: Coore Top / Suit, Ain Coat / Suit; размеры S–5XL, до 50 кг.</t>
-        </is>
-      </c>
+          <t>Не начаты</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Корейский ассортимент не только на мелких собак — редкость.</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Каталог 25SS получен. MOQ и прайс дистрибьютора — запросить.</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Контакт — в переписке у команды.</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
+          <t>Не найдено</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Ошейники, шлейки, поводки, намордники, одежда.</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Широкая линейка амуниции.</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Часть товара сделана в Китае — не «украинское производство».</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr"/>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr"/>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>https://e-zoo.com.ua/ua/139-amuniciya-dlya-sobak/f/12956-biotan</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>DIQPET</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Китай</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Шанхай</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Мелкие (до 8 кг)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>В переписке</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Urban Trekking Onesie: комбинезон на четыре лапы со встроенными ботинками. Есть отдельная линия на собак до 40 кг.</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Функциональная вещь для грязи и мокрого снега; поставщик честно описывает ограничения ткани.</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>MOQ 30 шт., размеры можно смешивать, один цвет. Образцы: 2 шт. Прайс и доставка — в ответе от 07.10.2026.</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Крой корейский: размеры меньше европейских, подбирать по обхвату груди. Ткань водоотталкивающая, не мембрана.</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr"/>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>Ответ DIQPET на 11 вопросов, 07.10.2026 (файл у команды)</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Merlot Studio</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Корея</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Одежда</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Все размеры</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>В переписке</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Одежда для собак: Coore Top / Suit, Ain Coat / Suit; размеры S–5XL, до 50 кг.</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Корейский ассортимент не только на мелких собак — редкость.</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Каталог 25SS получен. MOQ и прайс дистрибьютора — запросить.</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Контакт — в переписке у команды.</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>Каталог Merlot 25SS (файл у команды)</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V22"/>
+  <autoFilter ref="A1:AA24"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z7" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z8" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z9" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z10" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z11" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z12" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z13" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z14" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z16" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z17" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z18" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z19" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T20" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z20" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z21" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z22" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/suppliers.xlsx
+++ b/suppliers.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Поставщики" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Популярные товары" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Поставщики'!$A$1:$AA$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Поставщики'!$A$1:$AC$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Популярные товары'!$A$1:$F$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -61,7 +63,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -72,6 +74,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -451,22 +455,24 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="46" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
-    <col width="32" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="32" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,80 +533,90 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Отзывы и рейтинг</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Популярные товары</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Что делает</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Из поиска</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Условия и цены</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Заметка</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Каталог</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Etsy</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Telegram</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Проверено</t>
         </is>
@@ -660,68 +676,81 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>Rozetka: 268 отзывов на 103 товара. Etsy: 4,8 из 5 (252 отзыва), 836 продаж за 2,5 года.</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Куртка-дождевик Moss Yellow — 1 050 грн (105 отзывов, 4,6 · Rozetka)
+Пуховик Bobby Navy — 1 240 грн (97 отзывов, 4,8 · Rozetka)
+Комбинезон Travis — 1 790 грн (19 отзывов, 4,9 · Rozetka)
+Куртка-дождевик Moss Blue — 1 050 грн (13 отзывов, 4,6 · Rozetka)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>Одежда, лежаки и подушки, автогамаки для перевозки собак.</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Широкая линейка у одного производителя, невысокие цены.</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Запросить. Розница по статье 2021 года: одежда 330–640 грн, лежаки 400–2 000 грн.</t>
-        </is>
-      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
+          <t>Широкая линейка у одного производителя: одежда, лежаки, автогамаки.</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Опт — запросить. Розница сейчас: одежда 800–1 800 грн.</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
           <t>Уже продаёт за рубеж в розницу через Etsy.</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>https://noblepet.com.ua/</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>https://noblepet.com.ua/yak-zrobyty-zamiry/</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/noble_pet</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/noblepet.com.ua</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>https://www.etsy.com/shop/NoblePetStore</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>noblepetco@gmail.com</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>+380667836190</t>
         </is>
       </c>
-      <c r="Z2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -766,7 +795,7 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Не найдено</t>
+          <t>Отдельные магазины</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -781,56 +810,69 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
+          <t>Отзывов не нашли: раздел на сайте пуст, на Rozetka бренда нет. Порядок — «хиты продаж» с сайта.</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Поводок из облегчённого BioThane 3 м, для малых собак и кошек — 1 265 грн (хит продаж на сайте)
+Поводок из классического биотана 3 м, от 10 кг — 1 550 грн (хит продаж на сайте)
+Анатомическая шлейка из биотана S/M — 1 250 грн (первая в категории)
+Перестёжка «свободные руки» 3 м, до 10 кг — 1 620 грн (первая в категории)</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
           <t>Амуниция из биотана: перестёжки «свободные руки», поводки до и от 10 кг, анатомические шлейки, ошейники; ремонт поводков.</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Свой производитель биотановой амуниции — закрывает наше ядро: шлейки и поводки.</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Розница: перестёжка 1 620–2 333 грн. Опт — запросить по почте: раздел «Співпраця» приглашает к предложениям.</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>В соцсетях — @BioIntellectUA.</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Опт открыт: брендирование нашим логотипом, фурнитура из Чехии и Италии, ширина ленты 9, 16 и 19 мм; коммерческое предложение — по запросу. Розница: поводки 1 265–1 895 грн.</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>В соцсетях — @BioIntellectUA. Пишут об опыте работы с магазинами в Украине, Израиле и Испании.</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>https://biointellect.net/</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>https://biointellect.net/perestibky/</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>biointellectanimals@gmail.com</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>+380631079615</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>https://biointellect.net/spivpratsya/</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -894,64 +936,78 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Отзывов на сайте нет. Порядок — по числу продаж в их магазине.</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Биотановый поводок — от 407 грн (1-е место по продажам)
+Удавка 3–4 мм — от 181 грн (2-е место по продажам)
+Прорезиненный поводок — от 317 грн (3-е место по продажам)
+Сумка для лакомств с клипсой — от 271 грн (4-е место по продажам)
+Мяч «Дыня мини» — от 452 грн (5-е место по продажам)</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>Снаряжение для дрессировки: биотановые поводки и ошейники, шлейки, намордники, рукава и ухватки, инвентарь для следовой работы; одежда для кинологов.</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Профессиональный ассортимент для собачьего спорта; есть индивидуальный заказ.</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Опт — запросить. На сайте указано: работают по Украине и Европе.</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Проводят семинары и занятия в Киеве — близки нам по духу. Что шьют сами, а что перепродают — уточнить.</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>https://www.ipo4you.com.ua/ua/</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>https://www.ipo4you.com.ua/ua/shop/</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/ipo4you</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/260988080909100</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/channel/UCUZNYkwFYAoHf4dlhgjNi-Q</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>+380677062274</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>https://www.ipo4you.com.ua/ua/</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1011,60 +1067,74 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>Etsy: 4,8 из 5 (1,4 тыс. отзывов), 5 770 продаж за 10 лет. На своём сайте отзывов нет. На Etsy цены в 2–3 раза выше, чем на украинском сайте.</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Дождевик-комбинезон для таксы, по меркам — 448 zł (витрина магазина на Etsy)
+Дождевик в клетку (фланель) — 630 zł (витрина магазина на Etsy)
+Снуд для собак — 151 zł (витрина магазина на Etsy)
+Попона Perfect Match, мембрана, 24 размера — 1 980 грн (1-е место по популярности на сайте)
+Ромпер флисовый Hygge — 1 010 грн (3-е место по популярности на сайте)</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>Комбинезоны, куртки, попоны, жилеты, пыльники, охлаждающая коллекция; сумки для выгула и дождевик для владельца.</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>Около 10 лет на рынке. По подкасту SendPulse (июнь 2026) основательница выбирает дистрибьюторов и фокусные рынки — партнёра ищут сами.</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>Опт и минимальная партия — запросить. Пошив под заказ 5–7 рабочих дней.</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>На сайте есть раздел «Співпраця», но без условий.</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>https://barkandgo.com.ua/</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>https://barkandgo.com.ua/shop/sobaka/doschoviki-legki/</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>https://www.etsy.com/shop/BarkAndGo</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
       <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>info.barkandgo.ua@gmail.com</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>+380677494005</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>https://sendpulse.ua/blog/podkast-z-oleksandroiu-vakarovoiu</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1124,64 +1194,77 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>Rozetka: больше 1 000 товаров, но отзывов мало — 65 на 53 товара, не больше 3 на товар. Etsy: 4,0 из 5 (6 отзывов), 37 продаж, магазин на паузе с февраля 2026.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Костюм махровый — 625 грн (топ продаж на сайте)
+Рубашка в клетку — 580 грн (топ продаж на сайте)
+Дождевик с рюшами — 636 грн (3 отзыва, 5,0 · Rozetka)
+Жилет на липучках — 970 грн (3 отзыва, 5,0 · Rozetka)</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>Одежда с 2014 года, своя команда дизайнеров и швей; отдельные линейки для такс и корги.</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Доступная цена и породные лекала: дождевик-комбинезон для таксы около 680–920 грн в рознице.</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Опт и минимальная партия — запросить.</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Опт и дропшиппинг — по заявке через форму на сайте: после неё открывают оптовый каталог.</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>Дистрибьютора в ЕС поиск не нашёл.</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>https://dogsbomba.com/</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>https://dogsbomba.com/catalog/platya/</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/dogs_bomba</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>https://www.etsy.com/shop/DogsBomba</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
       <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>dogsbomba@gmail.com</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>+380996891029</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>https://dogsbomba.com/</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1245,56 +1328,69 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>Отзывов не нашли ни на сайте, ни на Rozetka. Порядок — по числу продаж в их магазине. Цены выше бюджетного сегмента.</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Тёплая куртка хаки — 1 800 грн (1-е место по продажам)
+Тёплая куртка «Пташки» — 2 100 грн (2-е место по продажам)
+Двусторонняя бандана — 300 грн (4-е место по продажам)
+Свитер «Догуфляж» — 1 200 грн (6-е место по продажам)</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>Куртки, дождевики, трикотаж, пледы; шьют с 2015 года.</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>Начинали с пошива по индивидуальным меркам — можно обсуждать нестандартные размеры.</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Опт — запросить. Розница по статье 2021 года: 700–1 300 грн.</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>Контакты на сайте не извлеклись, писать через Instagram.</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>https://www.woofitdogwear.com/</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>https://www.woofitdogwear.com/product-category/raincoats/</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/woofitdogwear</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/woofitdogwear/</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr"/>
-      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr"/>
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
+      <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1350,72 +1446,84 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>Отзывов не нашли. Порядок — отметки «топ продаж» на сайте.</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>ЭКО-пакеты из кукурузного крахмала — 170 грн (топ продаж на сайте)
+Универсальные пакеты для уборки — 100 грн (топ продаж на сайте)
+Пакеты серии «Put In»: 5 грн с упаковки идут UAnimals — 100 грн (топ продаж на сайте)</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>Пакеты для уборки: из кукурузного крахмала (домашнее компостирование) и обычные; контейнер для рулонов.</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Есть готовый «месячный запас» — наша механика расходников. Приглашают зоомагазины и салоны в партнёры.</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>Розница 100–170 грн за упаковку. Опт — запросить.</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>Сертификат компостируемости на главной не назван — запросить документ.</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>https://lavgav.ua/</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>https://lavgav.ua/faq</t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/welovegaw</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/welovegaw</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@welovegaw</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
+          <t>https://www.tiktok.com/@welovegaw</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
           <t>https://www.youtube.com/channel/UC6nuUqtOEUtWTPOajtu6E-Q</t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>welovegaw@gmail.com</t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>+380639351463</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>https://lavgav.ua/</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1475,76 +1583,88 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>Rozetka: 22 товара, 4 отзыва. На сайте 1 отзыв. Порядок — по числу продаж в их магазине.</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Лёгкие сушёные — от 144 грн (1-е место по продажам; 3 отзыва, 5,0 на Rozetka)
+Вымя сушёное кусочками — от 200 грн (2-е место по продажам)
+Рубец сушёный колбасками — от 116 грн (3-е место по продажам)</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>Сушёное мясо и субпродукты, один ингредиент в пачке, без добавок.</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>Сильный продукт для расходников.</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>Ввоз кормов животного происхождения в ЕС требует ветеринарных разрешений — пока вне нашей схемы.</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>https://vitameat.com.ua/</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="S9" s="3" t="inlineStr">
         <is>
           <t>https://vitameat.com.ua/product-category/susheni-kovbaski/</t>
         </is>
       </c>
-      <c r="R9" s="3" t="inlineStr">
+      <c r="T9" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/vitameat.kyiv</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/Vitameat</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@vitameat</t>
         </is>
       </c>
-      <c r="V9" s="3" t="inlineStr">
+      <c r="X9" s="3" t="inlineStr">
         <is>
           <t>https://t.me/vitameat</t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr">
+      <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@vitameat_kyiv</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>info@vitameat.com.ua</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>+380732839011</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
+      <c r="AB9" s="3" t="inlineStr">
         <is>
           <t>https://vitameat.com.ua/</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
+      <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1604,60 +1724,66 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>Данных нет: на Rozetka бренда нет, сайт не отдаёт список товаров.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>Сушёные говяжьи субпродукты: лёгкие, сердце, печень, рубец.</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>Простой состав без консервантов.</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>https://basic-food.shop/</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/basic.rivne</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t>https://t.me/basic_food_bot</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>info@basic-food.shop</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>+380976655442</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr">
         <is>
           <t>https://basic-food.shop/</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1713,60 +1839,73 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>Rozetka: 332 отзыва на 70 товаров из первой тысячи.</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Лежак Brig — 1 395 грн (39 отзывов, 5,0 · Rozetka)
+Комбинезон Rain — 746 грн (38 отзывов, 4,7 · Rozetka)
+Лежак Lux — 505 грн (38 отзывов, 4,7 · Rozetka)
+Комбинезон Cold — 565 грн (16 отзывов, 4,9 · Rozetka)</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>Комбинезоны, дождевики, жилеты, худи; отдельные лекала под таксу и другие породы.</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Попадает в нишу такс. У владельца (Suziria Group) уже есть канал в Польшу для корма Savory через Hovet.</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>Опт — через Suziria Brands, запросить. Розница: комбинезон для таксы около 620–960 грн.</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>Крупный производитель: эксклюзив маловероятен. Польского дистрибьютора одежды поиск не нашёл.</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>https://pet-fashion.com.ua/</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t>https://pet-fashion.com.ua/uk/60-dosshoviki-ta-vitrovki</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="T11" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/petfashion_tm</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/petfashion.tm</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr"/>
-      <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/channel/UCVrt1m3VlfDR0LVjD6ogkyA</t>
         </is>
       </c>
-      <c r="X11" s="2" t="inlineStr"/>
-      <c r="Y11" s="2" t="inlineStr"/>
-      <c r="Z11" s="3" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
         <is>
           <t>https://mind.ua/news/20266537-ukrayinska-suziria-brands-vihodit-na-rinki-polshchi-ta-niderlandiv</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
+      <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1830,44 +1969,50 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>Данных не нашли.</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>Одежда и аксессуары для собак и кошек, своё ателье, пошив по меркам.</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Премиальный сегмент: 1 500–3 000 грн за вещь (цены 2021 года).</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>Сайт montmorency.com.ua сейчас отдаёт 404 — проверить, работает ли бренд.</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/montmorency_for_pets</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr"/>
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
-      <c r="Z12" s="3" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
+      <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1931,64 +2076,70 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>Данных не нашли.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>Амуниция для служебных собак: шлейки, тактические ошейники и поводки, намордники, обувь, защита.</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Вариант для крупных и рабочих собак и собачьего спорта.</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>Опт не указан. В Европу отправляют по индивидуальной договорённости, 7–14 рабочих дней.</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>По сайту это магазин; уточнить, что шьют сами.</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>https://bronik9.com.ua/</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
+      <c r="S13" s="3" t="inlineStr">
         <is>
           <t>https://bronik9.com.ua/category/5268-nashijniki-ta-povodki</t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="T13" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/bronik_k9</t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/BronikK9</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr"/>
-      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr"/>
-      <c r="W13" s="3" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>https://youtube.com/@BroniK9</t>
         </is>
       </c>
-      <c r="X13" s="2" t="inlineStr"/>
-      <c r="Y13" s="2" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>+380981789756</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr">
+      <c r="AB13" s="3" t="inlineStr">
         <is>
           <t>https://bronik9.com.ua</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
+      <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2044,26 +2195,30 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>Данных не нашли.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>Профессиональная амуниция: несколько видов поводков и ошейников.</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Возможный источник поводков для дрессировки.</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>Неизвестно.</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>Сайт best4dogs.com.ua не открывается; команда смотрела страницу в каталоге Made in UA.</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="2" t="inlineStr"/>
@@ -2072,12 +2227,14 @@
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="3" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
         <is>
           <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/best-4-dogs/</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
+      <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2125,44 +2282,50 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>Данных не нашли.</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>Ошейники, поводки, шлейки; худи, дождевики, зимние жилеты.</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Один из немногих найденных украинских брендов именно амуниции.</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>Запросить. Цены 2021 года: поводок от 200 грн.</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>Сайт mrsnoopy.com не открывается — проверить, работает ли бренд.</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/mrsnoopythedog</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr"/>
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="3" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2210,26 +2373,30 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>Данных не нашли.</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>Мастерская: ошейники из натуральной кожи под размер и цвет.</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Кожаная амуниция ручной работы.</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>Неизвестно.</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>Контакты поиском не нашлись — искать в Instagram.</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr"/>
@@ -2238,12 +2405,14 @@
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="inlineStr"/>
-      <c r="Z16" s="3" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr">
         <is>
           <t>https://shotam.info/ukrains-ki-zootovary-top-10-vyrobnykiv-odiahu-budynochkiv-ta-smakolykiv-dlia-tvaryn/</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
+      <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2295,48 +2464,54 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>Данных не нашли.</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>Адресники с гравировкой телефона владельца, разные формы и размеры.</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Недорогое персональное дополнение к заказу.</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>Город — предположение по домену.</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>http://dogtag.kiev.ua</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/dogtag.kiev.ua</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr"/>
-      <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr"/>
       <c r="Y17" s="2" t="inlineStr"/>
-      <c r="Z17" s="3" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr">
         <is>
           <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/dogtag/</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2388,56 +2563,62 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>Данных не нашли.</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>Сушёные говяжьи субпродукты широкой линейкой; производитель — ТД «Едельвейс Україна».</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Работают оптом, большой ассортимент.</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>https://www.lasoshizsela.com/</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/lasochi_z_sela</t>
         </is>
       </c>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/1171886699563323</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr"/>
-      <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="inlineStr"/>
-      <c r="X18" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr"/>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>korma.zp.ua@gmail.com</t>
         </is>
       </c>
-      <c r="Y18" s="2" t="inlineStr"/>
-      <c r="Z18" s="3" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr">
         <is>
           <t>https://www.lasoshizsela.com/</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
+      <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2485,31 +2666,35 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>Данных не нашли.</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>Крафтовые сушёные лакомства из говядины.</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Небольшое производство, без консервантов.</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>То же ограничение: ветеринарные разрешения на ввоз. Сайт открывается с ошибкой сертификата.</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>https://snackon.com.ua/</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr"/>
       <c r="U19" s="2" t="inlineStr"/>
@@ -2517,12 +2702,14 @@
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr"/>
       <c r="Y19" s="2" t="inlineStr"/>
-      <c r="Z19" s="3" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr">
         <is>
           <t>https://snackon.com.ua/</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
+      <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2578,68 +2765,80 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>Rozetka: 382 отзыва на 38 товаров из первой тысячи.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Лежак Dreamer Brown M — 2 289 грн (97 отзывов, 4,8 · Rozetka)
+Лежак Dreamer Velvet M — 3 290 грн (55 отзывов, 5,0 · Rozetka)
+Миски на подставке Lunch Bar S — 2 890 грн (21 отзыв, 4,9 · Rozetka)</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>Лежаки, диваны, миски на подставке, автогамаки; немного амуниции.</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Известный бренд, но не наша стартовая категория.</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>Похоже, уже есть немецкий сайт — уникальности не будет.</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>https://harleyandcho.ua/</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/harleyandcho</t>
         </is>
       </c>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="U20" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/harleyandcho.main</t>
         </is>
       </c>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="V20" s="3" t="inlineStr">
         <is>
           <t>https://www.etsy.com/listing/584236455</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr"/>
-      <c r="V20" s="2" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr">
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr"/>
+      <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@HarleyandCho</t>
         </is>
       </c>
-      <c r="X20" s="2" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>info@harleyandcho.ua</t>
         </is>
       </c>
-      <c r="Y20" s="2" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>+380674527445</t>
         </is>
       </c>
-      <c r="Z20" s="3" t="inlineStr">
+      <c r="AB20" s="3" t="inlineStr">
         <is>
           <t>https://harleyandcho.ua/</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
+      <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2691,31 +2890,42 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>Rozetka: больше 7 000 отзывов по двум маркам; ниже — только товары для собак.</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Куртка AiryVest ONE — 969 грн (219 отзывов, 4,8 · Rozetka)
+Мячик Liker 7 — 95 грн (124 отзыва, 4,8 · Rozetka)
+Ошейник кожаный Waudog Classic — 224 грн (91 отзыв, 4,7 · Rozetka)
+Поводок Waudog Waterproof 3 м — 676 грн (75 отзывов, 4,8 · Rozetka)</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t>Ошейники, поводки, шлейки, адресники с QR, куртки AiryVest, Puller.</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Ориентир по качеству, а не поставщик для уникального ассортимента.</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>Опт в Польше — через COLLAR PL.</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>Продаётся в 70 странах, в Польше есть своя компания.</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>https://collar.com/</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
       <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr"/>
@@ -2723,12 +2933,14 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr"/>
       <c r="Y21" s="2" t="inlineStr"/>
-      <c r="Z21" s="3" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr">
         <is>
           <t>https://forbes.ua/company/eksperimenty-na-zhivotnykh-17022021-1037</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
+      <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2776,26 +2988,36 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>Rozetka: 542 отзыва на 143 товара из первой тысячи.</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Адресник из нержавеющей стали «Косточка» — 129 грн (77 отзывов, 4,9 · Rozetka)
+Адресник с гравировкой «Косточка» 40×25 мм — 129 грн (53 отзыва, 5,0 · Rozetka)
+Поводок брезентовый светоотражающий 5 м — 392 грн (20 отзывов, 5,0 · Rozetka)</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>Ошейники, шлейки, поводки, намордники, одежда.</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Широкая линейка амуниции.</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>Часть товара сделана в Китае — не «украинское производство».</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr"/>
@@ -2804,12 +3026,14 @@
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="inlineStr"/>
       <c r="Y22" s="2" t="inlineStr"/>
-      <c r="Z22" s="3" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr">
         <is>
           <t>https://e-zoo.com.ua/ua/139-amuniciya-dlya-sobak/f/12956-biotan</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
+      <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2861,26 +3085,30 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>Не проверяли.</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>Urban Trekking Onesie: комбинезон на четыре лапы со встроенными ботинками. Есть отдельная линия на собак до 40 кг.</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Функциональная вещь для грязи и мокрого снега; поставщик честно описывает ограничения ткани.</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>MOQ 30 шт., размеры можно смешивать, один цвет. Образцы: 2 шт. Прайс и доставка — в ответе от 07.10.2026.</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>Крой корейский: размеры меньше европейских, подбирать по обхвату груди. Ткань водоотталкивающая, не мембрана.</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr"/>
@@ -2889,12 +3117,14 @@
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr"/>
       <c r="Y23" s="2" t="inlineStr"/>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>Ответ DIQPET на 11 вопросов, 07.10.2026 (файл у команды)</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
+      <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2942,26 +3172,30 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>Не проверяли.</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>Одежда для собак: Coore Top / Suit, Ain Coat / Suit; размеры S–5XL, до 50 кг.</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Корейский ассортимент не только на мелких собак — редкость.</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>Каталог 25SS получен. MOQ и прайс дистрибьютора — запросить.</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>Контакт — в переписке у команды.</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr"/>
       <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr"/>
@@ -2970,104 +3204,1681 @@
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr"/>
       <c r="Y24" s="2" t="inlineStr"/>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>Каталог Merlot 25SS (файл у команды)</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA24"/>
+  <autoFilter ref="A1:AC24"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z3" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z4" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T5" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z5" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z6" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z7" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z8" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z9" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z10" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z11" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z12" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z13" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z14" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z16" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z17" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z18" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z19" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T20" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z20" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z21" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z22" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB7" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y8" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB8" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y9" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X10" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB10" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T11" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y11" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB11" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB12" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T13" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y13" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB13" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB14" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB16" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T18" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T20" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V20" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y20" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId84"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Приоритет</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Товар</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Отзывы и место</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Noble Pet</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Куртка-дождевик Moss Yellow</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1 050 грн</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>105 отзывов, 4,6 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/68802291/p68802291/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Noble Pet</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Пуховик Bobby Navy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1 240 грн</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>97 отзывов, 4,8 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/252786756/p252786756/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Noble Pet</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Комбинезон Travis</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1 790 грн</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>19 отзывов, 4,9 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/339618355/p339618355/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Noble Pet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Куртка-дождевик Moss Blue</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1 050 грн</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>13 отзывов, 4,6 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/252786746/p252786746/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BioIntellect</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Поводок из облегчённого BioThane 3 м, для малых собак и кошек</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1 265 грн</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>хит продаж на сайте</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>https://biointellect.net/povidets-z-polehshenoho-biothane-dlia-malykh-sobak-i-kotiv-3m/942/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BioIntellect</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Поводок из классического биотана 3 м, от 10 кг</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1 550 грн</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>хит продаж на сайте</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>https://biointellect.net/povidets-z-klasychnoho-biotanu-3m-dlia-sobak-vid-10-kh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BioIntellect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Анатомическая шлейка из биотана S/M</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1 250 грн</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>первая в категории</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>https://biointellect.net/anatomichni-shleiky/1062/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BioIntellect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Перестёжка «свободные руки» 3 м, до 10 кг</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1 620 грн</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>первая в категории</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>https://biointellect.net/perestibky/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IPO4YOU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Биотановый поводок</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>от 407 грн</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ipo4you.com.ua/ua/product/biotanovyj-povodok-1-10-m/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IPO4YOU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Удавка 3–4 мм</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>от 181 грн</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ipo4you.com.ua/ua/product/udavka-5-6mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IPO4YOU</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Прорезиненный поводок</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>от 317 грн</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ipo4you.com.ua/ua/product/prorezinennyj-povodok-1-10m/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IPO4YOU</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Сумка для лакомств с клипсой</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>от 271 грн</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ipo4you.com.ua/ua/product/sumka-dlya-lakomstv-na-lipkoj-lente/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IPO4YOU</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Первая очередь</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Мяч «Дыня мини»</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>от 452 грн</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>5-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ipo4you.com.ua/ua/product/kusalka-dynya-mini/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bark&amp;Go</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Дождевик-комбинезон для таксы, по меркам</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>448 zł</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>витрина магазина на Etsy</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/shop/BarkAndGo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bark&amp;Go</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Дождевик в клетку (фланель)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>630 zł</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>витрина магазина на Etsy</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/shop/BarkAndGo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bark&amp;Go</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Снуд для собак</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>151 zł</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>витрина магазина на Etsy</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/shop/BarkAndGo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bark&amp;Go</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Попона Perfect Match, мембрана, 24 размера</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1 980 грн</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1-е место по популярности на сайте</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>https://barkandgo.com.ua/shop/sobaka/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bark&amp;Go</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ромпер флисовый Hygge</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1 010 грн</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3-е место по популярности на сайте</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>https://barkandgo.com.ua/shop/sobaka/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Dogs Bomba</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Костюм махровый</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>625 грн</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>топ продаж на сайте</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>https://dogsbomba.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dogs Bomba</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Рубашка в клетку</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>580 грн</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>топ продаж на сайте</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>https://dogsbomba.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dogs Bomba</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Дождевик с рюшами</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>636 грн</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3 отзыва, 5,0 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/531643534/p531643534/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dogs Bomba</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Жилет на липучках</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>970 грн</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3 отзыва, 5,0 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/417762108/p417762108/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Woofit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Тёплая куртка хаки</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1 800 грн</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.woofitdogwear.com/product/tepla-kurtka-khaki/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Woofit</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Тёплая куртка «Пташки»</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2 100 грн</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.woofitdogwear.com/product/tepla-kurtka-iz-paternom-ptashky/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Woofit</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Двусторонняя бандана</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>300 грн</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>4-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.woofitdogwear.com/product/bandana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Woofit</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Свитер «Догуфляж»</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1 200 грн</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>6-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.woofitdogwear.com/product/sviter-dogufljazh-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ЛавГав</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ЭКО-пакеты из кукурузного крахмала</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>170 грн</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>топ продаж на сайте</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>https://lavgav.ua/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ЛавГав</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Универсальные пакеты для уборки</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>100 грн</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>топ продаж на сайте</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>https://lavgav.ua/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ЛавГав</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Пакеты серии «Put In»: 5 грн с упаковки идут UAnimals</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>100 грн</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>топ продаж на сайте</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>https://lavgav.ua/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Vitameat</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Лёгкие сушёные</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>от 144 грн</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1-е место по продажам; 3 отзыва, 5,0 на Rozetka</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>https://vitameat.com.ua/product/legeni-sushi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Vitameat</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Вымя сушёное кусочками</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>от 200 грн</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>https://vitameat.com.ua/product/vymya-shmatochky/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Vitameat</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Вторая очередь</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Рубец сушёный колбасками</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>от 116 грн</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3-е место по продажам</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>https://vitameat.com.ua/product/rubets-kovbaskamy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Pet Fashion</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Третья очередь</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Лежак Brig</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1 395 грн</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>39 отзывов, 5,0 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/548883678/p548883678/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Pet Fashion</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Третья очередь</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Комбинезон Rain</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>746 грн</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>38 отзывов, 4,7 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/548883321/p548883321/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Pet Fashion</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Третья очередь</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Лежак Lux</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>505 грн</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>38 отзывов, 4,7 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/425117229/p425117229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Pet Fashion</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Третья очередь</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Комбинезон Cold</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>565 грн</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>16 отзывов, 4,9 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/569534710/p569534710/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Harley&amp;Cho</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Лежак Dreamer Brown M</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2 289 грн</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>97 отзывов, 4,8 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/490423359/p490423359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Harley&amp;Cho</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Лежак Dreamer Velvet M</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3 290 грн</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>55 отзывов, 5,0 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/485596274/p485596274/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Harley&amp;Cho</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Миски на подставке Lunch Bar S</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2 890 грн</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>21 отзыв, 4,9 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/575716819/p575716819/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Collar / WAUDOG</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Куртка AiryVest ONE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>969 грн</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>219 отзывов, 4,8 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/422596260/p422596260/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Collar / WAUDOG</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Мячик Liker 7</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>95 грн</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>124 отзыва, 4,8 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/392251662/p392251662/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Collar / WAUDOG</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ошейник кожаный Waudog Classic</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>224 грн</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>91 отзыв, 4,7 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/569624830/p569624830/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Collar / WAUDOG</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Поводок Waudog Waterproof 3 м</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>676 грн</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>75 отзывов, 4,8 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/569423944/p569423944/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Bronzedog</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Адресник из нержавеющей стали «Косточка»</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>129 грн</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>77 отзывов, 4,9 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/87752392/p87752392/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Bronzedog</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Адресник с гравировкой «Косточка» 40×25 мм</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>129 грн</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>53 отзыва, 5,0 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/87752506/p87752506/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Bronzedog</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Без приоритета</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Поводок брезентовый светоотражающий 5 м</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>392 грн</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>20 отзывов, 5,0 · Rozetka</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>https://rozetka.com.ua/ua/305319368/p305319368/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F47"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/suppliers.xlsx
+++ b/suppliers.xlsx
@@ -3610,7 +3610,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>https://biointellect.net/perestibky/</t>
+          <t>https://biointellect.net/perestibka-dlia-sobak-do-10kh-3m/566/</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/shop/BarkAndGo</t>
+          <t>https://www.etsy.com/listing/4339958653/waterproof-dachshund-corgi-raincoat</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/shop/BarkAndGo</t>
+          <t>https://www.etsy.com/listing/4412229192/waterproof-dog-raincoat-tartan-flannel</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/shop/BarkAndGo</t>
+          <t>https://www.etsy.com/listing/4407849484/dog-snood-neck-warmer-for-all-dog-sizes</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>https://barkandgo.com.ua/shop/sobaka/</t>
+          <t>https://barkandgo.com.ua/shop/popona-dlya-sobak-perfect-match-pink-membrana-24-rozmiri/</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>https://barkandgo.com.ua/shop/sobaka/</t>
+          <t>https://barkandgo.com.ua/shop/romper-flisoviy-hygge/</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>https://dogsbomba.com/</t>
+          <t>https://dogsbomba.com/catalog/kostyum-makhrovyy-shokolad-d-271/</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>https://dogsbomba.com/</t>
+          <t>https://dogsbomba.com/catalog/rubashka-kletchataya-elektrik-rub-73/</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>https://lavgav.ua/</t>
+          <t>https://lavgav.ua/products/corn-bags</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>https://lavgav.ua/</t>
+          <t>https://lavgav.ua/products/universal_bio_bags</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>https://lavgav.ua/</t>
+          <t>https://lavgav.ua/products/putin_cleanup-bags</t>
         </is>
       </c>
     </row>

--- a/suppliers.xlsx
+++ b/suppliers.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Поставщики" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Популярные товары" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Письма" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Поставщики'!$A$1:$AC$24</definedName>
@@ -4882,4 +4883,158 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="110" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Канал</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Кому</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Тема</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Текст</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Noble Pet</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>noblepetco@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Гуртова співпраця — магазин для собак у Польщі</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день!
+Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
+Нам сподобалися ваші моделі та те, як докладно описані товари й заміри. Найбільше цікавлять дощовики Moss, пуховики Bobby та комбінезони Travis — зокрема через широку розмірну сітку з варіантами Long і Short.
+Підкажіть, будь ласка:
+1. Чи можете надіслати гуртовий каталог із цінами та мінімальним замовленням?
+2. Чи можна змішувати розміри в одному замовленні й замовити невеликий набір зразків?
+3. Чи маєте досвід гуртових відправлень до ЄС і які документи оформлюєте (експортна декларація, декларація про походження)?
+4. Чи можете надати склад тканин і дані про водовідштовхувальне просочення? Вони потрібні нам для маркування в ЄС.
+Нам зручно листуватися українською або англійською.
+Дякую і гарного дня!
+Дар'я [прізвище]
+[телефон, Instagram]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BioIntellect</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>biointellectanimals@gmail.com</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Гуртова співпраця — магазин для собак у Польщі</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день!
+Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин амуніції для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
+Амуніцію з BioThane ми знаємо з власного досвіду — вона служить роками. Прочитали вашу статтю про гуртове партнерство й хочемо обговорити співпрацю. Найбільше нас цікавлять повідці з полегшеного біотану для собак до 10 кг, класичні повідці, анатомічні шлейки та перестібки.
+Підкажіть, будь ласка:
+1. Чи можете надіслати комерційну пропозицію: гуртові ціни та мінімальне замовлення?
+2. Чи можна замовити невелику пробну партію або зразки?
+3. Чи маєте досвід відправлень до ЄС для магазинів і які документи оформлюєте (експортна декларація, декларація про походження)?
+4. Чи є у вас уже партнери в Польщі?
+5. Які умови брендування амуніції логотипом магазину?
+Нам зручно листуватися українською або англійською.
+Дякую і гарного дня!
+Дар'я [прізвище]
+[телефон, Instagram]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>IPO4YOU</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Мессенджер или Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>+380677062274</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день! Мене звати Дар'я, я кінологиня з Познані. Ми з командою запускаємо в Польщі інтернет-магазин амуніції для собак і шукаємо постачальника спорядження для дресирування.
+У вас нас цікавлять біотанові та слідові повідці, шлейки, сумки для ласощів та іграшки для тренувань.
+Підкажіть, будь ласка:
+1. Чи працюєте ви з магазинами гуртом і які умови: ціни, мінімальне замовлення?
+2. Що з асортименту ви виготовляєте самі?
+3. Чи відправляли вже замовлення до Польщі й які документи оформлюєте?
+На яку пошту зручно надіслати докладніший лист? Дякую!</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/suppliers.xlsx
+++ b/suppliers.xlsx
@@ -4891,7 +4891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5034,6 +5034,226 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Bark&amp;Go</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>info.barkandgo.ua@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Співпраця — магазин для собак у Польщі</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день!
+Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
+Ваші речі ми знаємо з сайту та Etsy: подобаються мембранні дощовики й комбінезони, велика розмірна сітка та пошив за мірками. Окремо цікаві дощовики для такс і парні образи «людина + собака».
+Підкажіть, будь ласка:
+1. Чи працюєте ви з магазинами-партнерами і на яких умовах: гуртові ціни, мінімальне замовлення?
+2. Чи можна працювати під замовлення — ми передаємо заміри клієнта, ви шиєте — і які тоді терміни?
+3. Чи можна замовити кілька зразків для примірки та зйомки?
+4. Чи маєте досвід гуртових відправлень до ЄС і які документи оформлюєте (експортна декларація, декларація про походження)?
+5. Чи є у вас уже партнери в Польщі?
+Нам зручно листуватися українською або англійською.
+Дякую і гарного дня!
+Дар'я [прізвище]
+[телефон, Instagram]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Dogs Bomba</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>dogsbomba@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Гуртова співпраця — магазин для собак у Польщі</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день!
+Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
+Нас цікавить ваш одяг за доступною ціною: насамперед дощовики й зимові комбінезони для такс, а також дощовики для великих собак.
+Підкажіть, будь ласка:
+1. Чи можете відкрити доступ до гуртового каталогу з цінами? Яке мінімальне замовлення?
+2. Чи можна змішувати моделі та розміри в одному замовленні?
+3. Чи маєте досвід гуртових відправлень до ЄС і які документи оформлюєте (експортна декларація, декларація про походження)?
+4. Чи можете надати склад тканин? Він потрібен нам для маркування в ЄС.
+Нам зручно листуватися українською або англійською.
+Дякую і гарного дня!
+Дар'я [прізвище]
+[телефон, Instagram]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Woofit</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woofitdogwear</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день! Мене звати Дар'я, я кінологиня з Познані. Ми з командою запускаємо в Польщі інтернет-магазин для собак. Нам подобаються ваші теплі куртки й дощовики та розмірна сітка за породами.
+Підкажіть, будь ласка:
+1. Чи працюєте ви з магазинами гуртом і на яких умовах?
+2. Які обсяги й терміни пошиву для вас реальні?
+3. Чи відправляли вже замовлення до Польщі?
+На яку пошту зручно надіслати докладніший лист? Дякую!</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ЛавГав</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>welovegaw@gmail.com</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Гуртова закупівля пакетів — магазин для собак у Польщі</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день!
+Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
+Шукаємо постачальника пакетів для прибирання за собаками. Нас цікавлять пакети з кукурудзяного крохмалю та формат «місячний запас».
+Підкажіть, будь ласка:
+1. Чи можете надіслати гуртові ціни та мінімальне замовлення? Скільки пакетів в упаковці, який розмір і товщина?
+2. Чи є сертифікат, що підтверджує придатність крохмальних пакетів до компостування (EN 13432, OK compost HOME або інший)?
+3. Який склад БІО-пакетів: це поліетилен із добавкою? Для нас це важливо через вимоги ЄС до оксорозкладного пластику.
+4. Чи маєте досвід гуртових відправлень до ЄС і які документи оформлюєте (експортна декларація, декларація про походження)?
+5. Чи можна замовити зразки?
+Нам зручно листуватися українською або англійською.
+Дякую і гарного дня!
+Дар'я [прізвище]
+[телефон, Instagram]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Vitameat</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>info@vitameat.com.ua</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Гуртова співпраця — магазин для собак у Польщі</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день!
+Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
+Нас цікавлять ваші сушені ласощі з одного інгредієнта: легені, рубець, ковбаски.
+Підкажіть, будь ласка:
+1. Чи маєте ви дозвіл на експорт до ЄС (підприємство в переліку затверджених ЄС для кормів тваринного походження) і чи вже постачаєте до країн ЄС?
+2. Чи можете надіслати гуртовий прайс і мінімальне замовлення?
+3. Який термін придатності та умови зберігання?
+4. Чи можете надати склад і аналітичні показники для маркування польською?
+Нам зручно листуватися українською або англійською.
+Дякую і гарного дня!
+Дар'я [прізвище]
+[телефон, Instagram]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BASIC.FOOD</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>info@basic-food.shop</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Гуртова співпраця — магазин для собак у Польщі</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день!
+Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
+Нас цікавлять ваші сушені яловичі субпродукти: легені, серце, печінка, рубець.
+Підкажіть, будь ласка:
+1. Чи маєте ви дозвіл на експорт до ЄС (підприємство в переліку затверджених ЄС для кормів тваринного походження) і чи вже постачаєте до країн ЄС?
+2. Чи можете надіслати гуртовий прайс і мінімальне замовлення?
+3. Який термін придатності та умови зберігання?
+4. Чи можете надати склад і аналітичні показники для маркування польською?
+Нам зручно листуватися українською або англійською.
+Дякую і гарного дня!
+Дар'я [прізвище]
+[телефон, Instagram]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/suppliers.xlsx
+++ b/suppliers.xlsx
@@ -4891,7 +4891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5254,6 +5254,89 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Pet Fashion</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Instagram или Facebook</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/petfashion_tm</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день! Мене звати Дар'я, я кінологиня з Познані. Ми з командою запускаємо в Польщі інтернет-магазин для собак і розглядаємо ваш одяг для асортименту: комбінезони COLD, дощовики RAIN, жилети.
+Підкажіть, будь ласка:
+1. Хто у вас відповідає за експорт і гуртові продажі за кордон?
+2. Чи є у Pet Fashion дистриб'ютор у Польщі?
+3. Чи можна отримати гуртовий прайс і умови для невеликого магазину?
+На яку пошту зручно надіслати докладніший лист? Дякую!</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Montmorency</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/montmorency_for_pets</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день! Мене звати Дар'я, я кінологиня з Познані. Ми з командою запускаємо в Польщі інтернет-магазин для собак. Бачили ваш одяг та пошив за мірками, але сайт зараз не відкривається.
+Підкажіть, будь ласка:
+1. Чи працює бренд зараз і де можна подивитися актуальний каталог?
+2. Чи співпрацюєте ви з магазинами?
+Дякую!</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>БроніК9</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Мессенджер или Instagram</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>+380981789756</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день! Мене звати Дар'я, я кінологиня з Познані. Ми з командою запускаємо в Польщі інтернет-магазин амуніції для собак. Нас цікавить амуніція для великих і робочих собак: шлейки К9, комплекти нашийник із повідцем, амортизаційні повідці.
+Підкажіть, будь ласка:
+1. Що з асортименту ви виготовляєте самі?
+2. Чи працюєте ви з магазинами гуртом і на яких умовах?
+3. Чи відправляли вже замовлення до Польщі й які документи оформлюєте?
+На яку пошту зручно надіслати докладніший лист? Дякую!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/suppliers.xlsx
+++ b/suppliers.xlsx
@@ -2688,7 +2688,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>То же ограничение: ветеринарные разрешения на ввоз. Сайт открывается с ошибкой сертификата.</t>
+          <t>То же ограничение: ветеринарные разрешения на ввоз. 13.10.2026 сайт не работает: домен без содержимого.</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2924,18 +2924,34 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>https://collar.com/</t>
+          <t>https://collar.pl/</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr"/>
-      <c r="U21" s="2" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/waudog.pl/</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/waudogpl</t>
+        </is>
+      </c>
       <c r="V21" s="2" t="inlineStr"/>
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr"/>
       <c r="Y21" s="2" t="inlineStr"/>
-      <c r="Z21" s="2" t="inlineStr"/>
-      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>info@waudog.pl</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>+48603742216</t>
+        </is>
+      </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
           <t>https://forbes.ua/company/eksperimenty-na-zhivotnykh-17022021-1037</t>
@@ -3303,8 +3319,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y20" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T21" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4891,7 +4909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5337,6 +5355,220 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Mr. Snoopy</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mrsnoopythedog</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день! Мене звати Дар'я, я кінологиня з Познані. Ми з командою запускаємо в Польщі інтернет-магазин амуніції для собак. Бачили ваші нашийники, повідці та шлейки, але сайт зараз не відкривається.
+Підкажіть, будь ласка:
+1. Чи працює бренд зараз і де можна подивитися актуальний каталог?
+2. Чи співпрацюєте ви з магазинами?
+Дякую!</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Ласощі з села</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>korma.zp.ua@gmail.com</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Гуртова співпраця — магазин для собак у Польщі</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день!
+Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
+Нас цікавлять ваші сушені яловичі субпродукти: рубець, легені, печінка, трахея.
+Підкажіть, будь ласка:
+1. Чи маєте ви дозвіл на експорт до ЄС (підприємство в переліку затверджених ЄС для кормів тваринного походження) і чи вже постачаєте до країн ЄС?
+2. Чи можете надіслати гуртовий прайс і мінімальне замовлення?
+3. Який термін придатності та умови зберігання?
+4. Чи можете надати склад і аналітичні показники для маркування польською?
+Нам зручно листуватися українською або англійською.
+Дякую і гарного дня!
+Дар'я [прізвище]
+[телефон, Instagram]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Harley&amp;Cho</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>info@harleyandcho.ua</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Співпраця — магазин для собак у Польщі</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Добрий день!
+Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
+Для розширення асортименту нас цікавлять ваші лежаки Dreamer та миски на підставці Lunch Bar.
+Підкажіть, будь ласка:
+1. Чи є у вас дистриб'ютор або склад у Польщі чи в ЄС?
+2. Які умови для магазинів у ЄС: гуртові ціни, мінімальне замовлення?
+3. Звідки відправляються замовлення і які документи ви оформлюєте?
+Нам зручно листуватися українською або англійською.
+Дякую і гарного дня!
+Дар'я [прізвище]
+[телефон, Instagram]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Collar / WAUDOG</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Почта, на польском</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>info@waudog.pl</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Współpraca hurtowa — nowy sklep internetowy dla psów</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Dzień dobry,
+nazywam się Daria, jestem trenerką psów z Poznania. Razem z zespołem uruchamiamy sklep internetowy z akcesoriami dla psów: niewielki asortyment, który sama polecam klientom, i sprzedaż przez sieć trenerów i groomerów.
+Interesują nas produkty WAUDOG i Collar: kurtki AiryVest, smycze Waterproof, obroże oraz zabawki Liker i Puller.
+Proszę o informację:
+1. Jakie są warunki współpracy hurtowej dla nowego sklepu internetowego: cennik, minimalne zamówienie, rabaty?
+2. Czy sprzedają Państwo z magazynu w Polsce i jaki jest czas dostawy?
+3. Czy możemy korzystać ze zdjęć i opisów produktów?
+Sklep jest na etapie uruchamiania.
+Z góry dziękuję i pozdrawiam
+Daria [nazwisko]
+[telefon, e-mail]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>DIQPET</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Почта, на английском</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nick, DIQPET — ответом в текущей переписке</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Re: Urban Trekking Onesie — follow-up questions</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nick,
+Thank you for the detailed reply and the size guide. They answered most of our questions, and we appreciate how openly you described the limits of the fabric.
+Before we decide on samples, could you clarify a few points?
+1. Can you confirm in writing that the DWR finish is free of PFHxA and other PFAS? The EU has restricted PFHxA in consumer clothing textiles since October 2026, and we want to be on the safe side.
+2. Under the DDP option, who acts as the importer of record in Poland? We need the import to be declared in our company's name, so we may prefer FOB or DAP with our own customs clearance.
+3. Can the Polish sticker label carry our company as the EU importer (name and address) and a batch or model number?
+4. Could you send the price list and MOQ for the large-size line (XS–XXXL)?
+5. Can the spray-rating test (AATCC 22) be done before a first order, and at what cost?
+Best regards,
+Darya [surname]
+[phone, email]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Merlot Studio</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Почта, на английском</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Merlot Studio — ответом в текущей переписке</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Merlot 25SS catalogue — distributor terms for Poland</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Hello,
+Thank you for sending the 25SS catalogue. We are a team from Poznań, Poland, launching an online dog shop built around a dog trainer's recommendations and a network of trainers and groomers. We are at the pre-launch stage and would like to start with samples.
+We are most interested in the Ain Coat, the Ain Suit and the Coore line. A size range up to 5XL is rare among Korean brands.
+Could you tell us:
+1. What are your distributor prices and minimum order? Can sizes be mixed in one order?
+2. What are the terms for a sample order?
+3. Do you already have a distributor in Poland or elsewhere in the EU, and what are your conditions for exclusivity?
+4. Can you issue an origin declaration under the EU–Korea free trade agreement?
+5. Can you share the fabric composition and confirm that the water-repellent finish is PFAS-free? We need this for EU labelling.
+Best regards,
+Darya [surname]
+[phone, email]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/suppliers.xlsx
+++ b/suppliers.xlsx
@@ -4909,7 +4909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5355,220 +5355,6 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Mr. Snoopy</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/mrsnoopythedog</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Добрий день! Мене звати Дар'я, я кінологиня з Познані. Ми з командою запускаємо в Польщі інтернет-магазин амуніції для собак. Бачили ваші нашийники, повідці та шлейки, але сайт зараз не відкривається.
-Підкажіть, будь ласка:
-1. Чи працює бренд зараз і де можна подивитися актуальний каталог?
-2. Чи співпрацюєте ви з магазинами?
-Дякую!</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Ласощі з села</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Почта</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>korma.zp.ua@gmail.com</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Гуртова співпраця — магазин для собак у Польщі</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Добрий день!
-Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
-Нас цікавлять ваші сушені яловичі субпродукти: рубець, легені, печінка, трахея.
-Підкажіть, будь ласка:
-1. Чи маєте ви дозвіл на експорт до ЄС (підприємство в переліку затверджених ЄС для кормів тваринного походження) і чи вже постачаєте до країн ЄС?
-2. Чи можете надіслати гуртовий прайс і мінімальне замовлення?
-3. Який термін придатності та умови зберігання?
-4. Чи можете надати склад і аналітичні показники для маркування польською?
-Нам зручно листуватися українською або англійською.
-Дякую і гарного дня!
-Дар'я [прізвище]
-[телефон, Instagram]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Harley&amp;Cho</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Почта</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>info@harleyandcho.ua</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Співпраця — магазин для собак у Польщі</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Добрий день!
-Мене звати Дар'я, я кінологиня з Познані. Разом із командою ми запускаємо в Польщі інтернет-магазин для собак: невеликий асортимент, який я сама рекомендую клієнтам, і продаж через мережу кінологів та грумерів.
-Для розширення асортименту нас цікавлять ваші лежаки Dreamer та миски на підставці Lunch Bar.
-Підкажіть, будь ласка:
-1. Чи є у вас дистриб'ютор або склад у Польщі чи в ЄС?
-2. Які умови для магазинів у ЄС: гуртові ціни, мінімальне замовлення?
-3. Звідки відправляються замовлення і які документи ви оформлюєте?
-Нам зручно листуватися українською або англійською.
-Дякую і гарного дня!
-Дар'я [прізвище]
-[телефон, Instagram]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Collar / WAUDOG</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Почта, на польском</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>info@waudog.pl</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Współpraca hurtowa — nowy sklep internetowy dla psów</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Dzień dobry,
-nazywam się Daria, jestem trenerką psów z Poznania. Razem z zespołem uruchamiamy sklep internetowy z akcesoriami dla psów: niewielki asortyment, który sama polecam klientom, i sprzedaż przez sieć trenerów i groomerów.
-Interesują nas produkty WAUDOG i Collar: kurtki AiryVest, smycze Waterproof, obroże oraz zabawki Liker i Puller.
-Proszę o informację:
-1. Jakie są warunki współpracy hurtowej dla nowego sklepu internetowego: cennik, minimalne zamówienie, rabaty?
-2. Czy sprzedają Państwo z magazynu w Polsce i jaki jest czas dostawy?
-3. Czy możemy korzystać ze zdjęć i opisów produktów?
-Sklep jest na etapie uruchamiania.
-Z góry dziękuję i pozdrawiam
-Daria [nazwisko]
-[telefon, e-mail]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>DIQPET</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Почта, на английском</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Nick, DIQPET — ответом в текущей переписке</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Re: Urban Trekking Onesie — follow-up questions</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Hi Nick,
-Thank you for the detailed reply and the size guide. They answered most of our questions, and we appreciate how openly you described the limits of the fabric.
-Before we decide on samples, could you clarify a few points?
-1. Can you confirm in writing that the DWR finish is free of PFHxA and other PFAS? The EU has restricted PFHxA in consumer clothing textiles since October 2026, and we want to be on the safe side.
-2. Under the DDP option, who acts as the importer of record in Poland? We need the import to be declared in our company's name, so we may prefer FOB or DAP with our own customs clearance.
-3. Can the Polish sticker label carry our company as the EU importer (name and address) and a batch or model number?
-4. Could you send the price list and MOQ for the large-size line (XS–XXXL)?
-5. Can the spray-rating test (AATCC 22) be done before a first order, and at what cost?
-Best regards,
-Darya [surname]
-[phone, email]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Merlot Studio</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Почта, на английском</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Merlot Studio — ответом в текущей переписке</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Merlot 25SS catalogue — distributor terms for Poland</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Hello,
-Thank you for sending the 25SS catalogue. We are a team from Poznań, Poland, launching an online dog shop built around a dog trainer's recommendations and a network of trainers and groomers. We are at the pre-launch stage and would like to start with samples.
-We are most interested in the Ain Coat, the Ain Suit and the Coore line. A size range up to 5XL is rare among Korean brands.
-Could you tell us:
-1. What are your distributor prices and minimum order? Can sizes be mixed in one order?
-2. What are the terms for a sample order?
-3. Do you already have a distributor in Poland or elsewhere in the EU, and what are your conditions for exclusivity?
-4. Can you issue an origin declaration under the EU–Korea free trade agreement?
-5. Can you share the fabric composition and confirm that the water-repellent finish is PFAS-free? We need this for EU labelling.
-Best regards,
-Darya [surname]
-[phone, email]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/suppliers.xlsx
+++ b/suppliers.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Письма" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Поставщики'!$A$1:$AC$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Популярные товары'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Поставщики'!$A$1:$AF$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Популярные товары'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AF23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -456,24 +456,27 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="46" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="46" customWidth="1" min="14" max="14"/>
-    <col width="46" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="34" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="32" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="24" customWidth="1" min="24" max="24"/>
-    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="17" max="17"/>
+    <col width="46" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="32" customWidth="1" min="25" max="25"/>
     <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="40" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="40" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,90 +537,105 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Сверка с концепцией</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Наборы</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Сверка: пояснение</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Отзывы и рейтинг</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Популярные товары</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Что делает</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Из поиска</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Условия и цены</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Заметка</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Каталог</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Etsy</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Telegram</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Проверено</t>
         </is>
@@ -677,10 +695,25 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>Хорошо</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Сезон, Щенок дома</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Сезонный набор для собак любого размера: сетка до 6XL с вариантами Long и Short — это наш подбор по телосложению, спрос подтверждён отзывами. Лежак и сумка-коврик идут в набор «Щенок дома». Размеры брать по реальному спросу, не всей сеткой.</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>Rozetka: 268 отзывов на 103 товара. Etsy: 4,8 из 5 (252 отзыва), 836 продаж за 2,5 года.</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Куртка-дождевик Moss Yellow — 1 050 грн (105 отзывов, 4,6 · Rozetka)
 Пуховик Bobby Navy — 1 240 грн (97 отзывов, 4,8 · Rozetka)
@@ -688,70 +721,70 @@
 Куртка-дождевик Moss Blue — 1 050 грн (13 отзывов, 4,6 · Rozetka)</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Одежда, лежаки и подушки, автогамаки для перевозки собак.</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Широкая линейка у одного производителя: одежда, лежаки, автогамаки.</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Интересные позиции (розница в Украине): дождевик от 990 грн, комбинезон от 1 650 грн, сумка-коврик Travel 1 300 грн. Магазинам и салонам обещают спецусловия, фото и печатные материалы; есть каталог для скачивания.</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Уже продаёт за рубеж в розницу через Etsy. В подвале сайта стоит 2014–2022 — проверить, что бренд работает.</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>https://noblepet.com.ua/</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>https://noblepet.com.ua/yak-zrobyty-zamiry/</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/noble_pet</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/noblepet.com.ua</t>
         </is>
       </c>
-      <c r="V2" s="3" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>https://www.etsy.com/shop/NoblePetStore</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>noblepetco@gmail.com</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>+380667836190</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr">
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -811,10 +844,25 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
+          <t>Хорошо</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Щенок дома, Городские прогулки, Занятия с кинологом</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Основа трёх наборов: облегчённый поводок, ошейник и шлейка для щенка, перестёжка для города, длинный поводок для занятий. У поводков почти нет размеров — деньги не замораживаются. Проверить цену: оптовой мы не знаем.</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
           <t>Отзывов не нашли: раздел на сайте пуст, на Rozetka бренда нет. Порядок — «хиты продаж» с сайта.</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Поводок из облегчённого BioThane 3 м, для малых собак и кошек — 1 265 грн (хит продаж на сайте)
 Поводок из классического биотана 3 м, от 10 кг — 1 550 грн (хит продаж на сайте)
@@ -822,58 +870,58 @@
 Перестёжка «свободные руки» 3 м, до 10 кг — 1 620 грн (первая в категории)</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>Амуниция из оригинального BioThane®: поводки 2–5 м (облегчённые для собак до 10 кг и классические), перестёжки «свободные руки», анатомические шлейки, ошейники; светоотражающие банданы, жёлтые маркеры настроения.</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Закрывает ядро ассортимента — поводки, шлейки, ошейники. Фурнитура из Чехии и Италии, отдельная облегчённая линейка для мелких собак. Сами зовут в опт и готовы брендировать амуницию логотипом партнёра.</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>Интересные позиции (розница в Украине): поводок облегчённый 3 м для собак до 10 кг 1 265 грн, поводок классический 3 м 1 550 грн, перестёжка 1 620–2 333 грн, анатомическая шлейка 1 150–1 350 грн, ошейник 400–915 грн, бандана светоотражающая 255 грн. Опт: гибкие условия, коммерческое предложение по запросу.</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>По их словам, уже работают с магазинами в Украине, Израиле и Испании — эксклюзив в ЕС уточнить. Ширина ленты 9, 16 и 19 мм.</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>https://biointellect.net/</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>https://biointellect.net/perestibky/</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>biointellectanimals@gmail.com</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>+380631079615</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>https://biointellect.net/hurtova-spivpratsia-z-biointellect/</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="inlineStr">
+      <c r="AF3" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -937,10 +985,25 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Хорошо</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Занятия с кинологом, Щенок дома</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Закрывает набор для занятий: сумка для лакомств, игрушки, длинные и следовые поводки. Их недорогой поводок — доступный вариант рядом с BioIntellect. Удавки и строгие ошейники не берём: расходятся с тоном бренда.</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>Отзывов на сайте нет. Порядок — по числу продаж в их магазине.</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Биотановый поводок — от 407 грн (1-е место по продажам)
 Удавка 3–4 мм — от 181 грн (2-е место по продажам)
@@ -949,66 +1012,66 @@
 Мяч «Дыня мини» — от 452 грн (5-е место по продажам)</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Снаряжение для дрессировки и спорта с собакой: биотановые и паракордовые поводки, следовые поводки и шлейки, кожаные шлейки и ошейники, шлейка ASTA; одежда для кинологов, аджилити-инвентарь.</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Амуниция для дрессировки — то, что рекомендуют кинологи; команда сама ведёт занятия и семинары. Есть раздел индивидуального заказа.</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Интересные позиции (розница в Украине): биотановый поводок с ручкой 452–1 267 грн, биотановый круглый поводок 498–1 674 грн, следовой поводок 10 м 1 357–1 448 грн, паракордовый поводок 163–362 грн, шлейка ASTA 1 403–1 629 грн, кожаная шлейка 1 674 грн. Опт — запросить.</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Что производят сами, а что перепродают — на сайте не указано, уточнить.</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>https://www.ipo4you.com.ua/ua/</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>https://www.ipo4you.com.ua/ua/shop/</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/ipo4you</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/260988080909100</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/channel/UCUZNYkwFYAoHf4dlhgjNi-Q</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr"/>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr">
         <is>
           <t>+380677062274</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>https://www.ipo4you.com.ua/</t>
         </is>
       </c>
-      <c r="AC4" s="2" t="inlineStr">
+      <c r="AF4" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1068,10 +1131,25 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>С оговорками</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Сезон, Городские прогулки</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Дождевики по меркам и лекала под таксу — в сезонный набор и в нишу такс; работа под заказ не требует склада. Сумочка для лакомств и диспенсер пакетов — в городской набор. Против: пёстрый дизайн и парные образы «человек + собака» не про «сначала собака».</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>Etsy: 4,8 из 5 (1,4 тыс. отзывов), 5 770 продаж за 10 лет. На своём сайте отзывов нет. На Etsy цены в 2–3 раза выше, чем на украинском сайте.</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>Дождевик-комбинезон для таксы, по меркам — 448 zł (витрина магазина на Etsy)
 Дождевик в клетку (фланель) — 630 zł (витрина магазина на Etsy)
@@ -1080,62 +1158,62 @@
 Ромпер флисовый Hygge — 1 010 грн (3-е место по популярности на сайте)</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>Мембранные комбинезоны, куртки и попоны, жилеты, пыльники, охлаждающая коллекция; сумки для выгула, сумочки для лакомств, диспенсер для пакетов, дождевик для владельца.</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Около 10 лет на рынке. По подкасту SendPulse (июнь 2026) основательница выбирает дистрибьюторов и фокусные рынки — партнёра ищут сами.</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Интересные позиции (розница в Украине): мембранный комбинезон 2 116–2 785 грн (29 размеров), мембранная попона 1 980 грн (24 размера), сумочка для лакомств 600–700 грн, диспенсер для пакетов 350 грн. Пошив под заказ 5–7 рабочих дней. Опт и минимальная партия — запросить.</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>На сайте есть раздел «Співпраця», но без условий. Большая размерная сетка и пошив под заказ позволяют продавать по замерам без склада.</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>https://barkandgo.com.ua/</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>https://barkandgo.com.ua/shop/sobaka/doschoviki-legki/</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.etsy.com/shop/BarkAndGo</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/shop/BarkAndGo</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>info.barkandgo.ua@gmail.com</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AD5" s="2" t="inlineStr">
         <is>
           <t>+380677494005</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr">
+      <c r="AE5" s="3" t="inlineStr">
         <is>
           <t>https://sendpulse.ua/blog/podkast-z-oleksandroiu-vakarovoiu</t>
         </is>
       </c>
-      <c r="AC5" s="2" t="inlineStr">
+      <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1195,10 +1273,25 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>С оговорками</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Сезон</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Доступный вариант в сезонном наборе: «можно купить дороже, но эта вещь тоже решает задачу», есть линейки для такс. В карточке честно писать, что ткань — плащёвка, не мембрана. Платья и костюмы не берём.</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>Rozetka: больше 1 000 товаров, но отзывов мало — 65 на 53 товара, не больше 3 на товар. Etsy: 4,0 из 5 (6 отзывов), 37 продаж, магазин на паузе с февраля 2026.</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Костюм махровый — 625 грн (топ продаж на сайте)
 Рубашка в клетку — 580 грн (топ продаж на сайте)
@@ -1206,66 +1299,66 @@
 Жилет на липучках — 970 грн (3 отзыва, 5,0 · Rozetka)</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>Одежда с 2014 года, своя команда дизайнеров и швей; отдельные линейки для такс и корги.</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Доступная цена и породные лекала: дождевик-комбинезон для таксы около 680–920 грн в рознице.</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Интересные позиции (розница в Украине): дождевик для такс 545–745 грн, зимний комбинезон для такс 920 грн, дождевик со шлейкой 920 грн, дождевик для крупных собак 1 175 грн, поводок Hands Free 510 грн. Опт и дропшиппинг — через форму на сайте, условия запросить.</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>Ткань дождевиков — водоотталкивающая плащёвка, не мембрана. Дистрибьютора в ЕС поиск не нашёл.</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>https://dogsbomba.com/</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>https://dogsbomba.com/catalog/platya/</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/dogs_bomba</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>https://www.etsy.com/shop/DogsBomba</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr"/>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>dogsbomba@gmail.com</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AD6" s="2" t="inlineStr">
         <is>
           <t>+380996891029</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>https://dogsbomba.com/</t>
         </is>
       </c>
-      <c r="AC6" s="2" t="inlineStr">
+      <c r="AF6" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1329,10 +1422,25 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>Слабо</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Сезон</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Повторяет роль Noble Pet и Bark&amp;Go без своего преимущества: небольшое ателье, отзывов нет, цена не ниже.</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>Отзывов не нашли ни на сайте, ни на Rozetka. Порядок — по числу продаж в их магазине. Цены выше бюджетного сегмента.</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Тёплая куртка хаки — 1 800 грн (1-е место по продажам)
 Тёплая куртка «Пташки» — 2 100 грн (2-е место по продажам)
@@ -1340,58 +1448,58 @@
 Свитер «Догуфляж» — 1 200 грн (6-е место по продажам)</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>Небольшое ателье: дождевики, лёгкие и тёплые куртки, жилеты, свитеры, бомберы; своя размерная сетка по породам, правка под размер.</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>Начинали с пошива по индивидуальным меркам — можно обсуждать нестандартные размеры.</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>Интересные позиции (розница в Украине): дождевик 1 300–1 500 грн, тёплая куртка 1 800–2 100 грн. Опт — запросить.</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>Почта на сайте скрыта защитой, писать через Instagram. Объёмы ателье небольшие.</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>https://www.woofitdogwear.com/</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>https://www.woofitdogwear.com/product-category/raincoats/</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/woofitdogwear</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/woofitdogwear/</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr">
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
         </is>
       </c>
-      <c r="AC7" s="2" t="inlineStr">
+      <c r="AF7" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1447,84 +1555,99 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>С оговорками</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Расходники, Щенок дома, Городские прогулки</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Пакеты входят в каждый набор и в напоминания о пополнении. Берём только крахмальные и только с сертификатом. Серия «Put In» расходится с нашим «без лозунгов».</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>Отзывов не нашли. Порядок — отметки «топ продаж» на сайте.</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>ЭКО-пакеты из кукурузного крахмала — 170 грн (топ продаж на сайте)
 Универсальные пакеты для уборки — 100 грн (топ продаж на сайте)
 Пакеты серии «Put In»: 5 грн с упаковки идут UAnimals — 100 грн (топ продаж на сайте)</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>Пакеты для уборки: из кукурузного крахмала (домашнее компостирование) и обычные; контейнер для рулонов.</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Есть готовый «месячный запас» — наша механика расходников. Приглашают зоомагазины и салоны в партнёры.</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Интересные позиции (розница в Украине): «месячный запас» пакетов из кукурузного крахмала 130 грн, крахмальные пакеты 150–170 грн, контейнер для рулонов 80 грн. Опт — запросить.</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>Пакеты «БИО» — полиэтилен с добавкой-биодеградантом: проверить, не подпадают ли под запрет ЕС на оксоразлагаемый пластик, до проверки не брать. Сертификат компостируемости крахмальных пакетов на сайте не назван — запросить документ.</t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>https://lavgav.ua/</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="V8" s="3" t="inlineStr">
         <is>
           <t>https://lavgav.ua/faq</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="W8" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/welovegaw</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="X8" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/welovegaw</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="3" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@welovegaw</t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/channel/UC6nuUqtOEUtWTPOajtu6E-Q</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
+      <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>welovegaw@gmail.com</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AD8" s="2" t="inlineStr">
         <is>
           <t>+380639351463</t>
         </is>
       </c>
-      <c r="AB8" s="3" t="inlineStr">
+      <c r="AE8" s="3" t="inlineStr">
         <is>
           <t>https://lavgav.ua/</t>
         </is>
       </c>
-      <c r="AC8" s="2" t="inlineStr">
+      <c r="AF8" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1584,88 +1707,103 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>Ждём ответа</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Занятия с кинологом, Щенок дома, Расходники</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Лакомства нужны в наборе для занятий и в наборе щенка. Всё решает ответ про разрешение на экспорт в ЕС: без него ввоз невозможен.</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>Rozetka: 22 товара, 4 отзыва. На сайте 1 отзыв. Порядок — по числу продаж в их магазине.</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>Лёгкие сушёные — от 144 грн (1-е место по продажам; 3 отзыва, 5,0 на Rozetka)
 Вымя сушёное кусочками — от 200 грн (2-е место по продажам)
 Рубец сушёный колбасками — от 116 грн (3-е место по продажам)</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>Сушёное мясо и субпродукты, один ингредиент в пачке, без добавок.</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>Сильный продукт для расходников.</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>Ввоз кормов животного происхождения в ЕС требует ветеринарных разрешений — пока вне нашей схемы.</t>
         </is>
       </c>
-      <c r="R9" s="3" t="inlineStr">
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>https://vitameat.com.ua/</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="V9" s="3" t="inlineStr">
         <is>
           <t>https://vitameat.com.ua/product-category/susheni-kovbaski/</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="W9" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/vitameat.kyiv</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="X9" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/Vitameat</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@vitameat</t>
         </is>
       </c>
-      <c r="X9" s="3" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>https://t.me/vitameat</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="AB9" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@vitameat_kyiv</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>info@vitameat.com.ua</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
+      <c r="AD9" s="2" t="inlineStr">
         <is>
           <t>+380732839011</t>
         </is>
       </c>
-      <c r="AB9" s="3" t="inlineStr">
+      <c r="AE9" s="3" t="inlineStr">
         <is>
           <t>https://vitameat.com.ua/</t>
         </is>
       </c>
-      <c r="AC9" s="2" t="inlineStr">
+      <c r="AF9" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1725,66 +1863,81 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>Ждём ответа</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Занятия с кинологом, Щенок дома, Расходники</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Лакомства нужны в наборе для занятий и в наборе щенка. Всё решает ответ про разрешение на экспорт в ЕС: без него ввоз невозможен.</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>Данных нет: на Rozetka бренда нет, сайт не отдаёт список товаров.</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>Сушёные говяжьи субпродукты: лёгкие, сердце, печень, рубец.</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Простой состав без консервантов.</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>https://basic-food.shop/</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/basic.rivne</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>https://t.me/basic_food_bot</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr"/>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>info@basic-food.shop</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AD10" s="2" t="inlineStr">
         <is>
           <t>+380976655442</t>
         </is>
       </c>
-      <c r="AB10" s="3" t="inlineStr">
+      <c r="AE10" s="3" t="inlineStr">
         <is>
           <t>https://basic-food.shop/</t>
         </is>
       </c>
-      <c r="AC10" s="2" t="inlineStr">
+      <c r="AF10" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1838,12 +1991,15 @@
           <t>Искать только товары с конкурентной ценой или интересными условиями опта.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Rozetka: 332 отзыва на 70 товаров из первой тысячи.</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>Лежак Brig — 1 395 грн (39 отзывов, 5,0 · Rozetka)
 Комбинезон Rain — 746 грн (38 отзывов, 4,7 · Rozetka)
@@ -1851,62 +2007,62 @@
 Комбинезон Cold — 565 грн (16 отзывов, 4,9 · Rozetka)</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>Комбинезоны, дождевики, жилеты, худи; отдельные лекала под таксу и другие породы.</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Попадает в нишу такс. У владельца (Suziria Group) уже есть канал в Польшу для корма Savory через Hovet.</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Интересные позиции (розница в Украине): комбинезон COLD 564–593 грн, дождевик RAIN 553–640 грн, жилет E.Vest 541–649 грн, светоотражающий Yellow Vest 354 грн, комбинезон Milly с размерами под корги 1 215 грн. Размеры до 7XL. Опт — через Suziria Brands, запросить.</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>Крупный производитель: эксклюзив маловероятен. Лекала под таксу при проверке сайта 12.10.2026 не подтверждены.</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>https://pet-fashion.com.ua/</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="V11" s="3" t="inlineStr">
         <is>
           <t>https://pet-fashion.com.ua/uk/60-dosshoviki-ta-vitrovki</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="W11" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/petfashion_tm</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="X11" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/petfashion.tm</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr"/>
-      <c r="W11" s="2" t="inlineStr"/>
-      <c r="X11" s="2" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCVrt1m3VlfDR0LVjD6ogkyA</t>
-        </is>
-      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="3" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/channel/UCVrt1m3VlfDR0LVjD6ogkyA</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
           <t>https://mind.ua/news/20266537-ukrayinska-suziria-brands-vihodit-na-rinki-polshchi-ta-niderlandiv</t>
         </is>
       </c>
-      <c r="AC11" s="2" t="inlineStr">
+      <c r="AF11" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -1968,52 +2124,55 @@
           <t>Проверить, работает ли бренд сейчас и актуальны ли контакты.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Данных не нашли.</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>Одежда и аксессуары для собак и кошек, своё ателье, пошив по меркам.</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Премиальный сегмент: 1 500–3 000 грн за вещь (цены 2021 года).</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>Сайт montmorency.com.ua сейчас отдаёт 404 — проверить, работает ли бренд.</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/montmorency_for_pets</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr"/>
-      <c r="W12" s="2" t="inlineStr"/>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/montmorency_for_pets</t>
+        </is>
+      </c>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr">
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
         </is>
       </c>
-      <c r="AC12" s="2" t="inlineStr">
+      <c r="AF12" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2075,72 +2234,75 @@
           <t>Узкая профессиональная ниша, не для основного ассортимента.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Данных не нашли.</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>Магазин амуниции для служебных собак: шлейки, тактические ошейники и поводки, намордники, обувь, защита. Большая часть — чужие бренды (OneTigris, Letsperfect, норвежская амуниция).</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Вариант для крупных и рабочих собак и собачьего спорта.</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Похоже на своё производство (уточнить): шлейки К9 1 655 и 2 510 грн, комплект К9 ошейник с поводком 845 грн, амортизирующий поводок 440 грн. Опт не указан. В Европу отправляют по индивидуальной договорённости, 7–14 рабочих дней.</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>Что шьют сами — по сайту не видно, вывод сделан по названиям товаров.</t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>https://bronik9.com.ua/</t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t>https://bronik9.com.ua/category/5268-nashijniki-ta-povodki</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="W13" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/bronik_k9</t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr">
+      <c r="X13" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/BronikK9</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr"/>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="2" t="inlineStr"/>
-      <c r="Y13" s="3" t="inlineStr">
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
         <is>
           <t>https://youtube.com/@BroniK9</t>
         </is>
       </c>
-      <c r="Z13" s="2" t="inlineStr"/>
-      <c r="AA13" s="2" t="inlineStr">
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr">
         <is>
           <t>+380981789756</t>
         </is>
       </c>
-      <c r="AB13" s="3" t="inlineStr">
+      <c r="AE13" s="3" t="inlineStr">
         <is>
           <t>https://bronik9.com.ua</t>
         </is>
       </c>
-      <c r="AC13" s="2" t="inlineStr">
+      <c r="AF13" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2194,35 +2356,35 @@
           <t>Низкий приоритет.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Данных не нашли.</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>Профессиональная амуниция: несколько видов поводков и ошейников.</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Возможный источник поводков для дрессировки.</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Неизвестно.</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>Сайт best4dogs.com.ua не открывается; команда смотрела страницу в каталоге Made in UA.</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="2" t="inlineStr"/>
@@ -2230,12 +2392,15 @@
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr">
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
         <is>
           <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/best-4-dogs/</t>
         </is>
       </c>
-      <c r="AC14" s="2" t="inlineStr">
+      <c r="AF14" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2281,52 +2446,55 @@
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Данных не нашли.</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>Ошейники, поводки, шлейки; худи, дождевики, зимние жилеты.</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>Один из немногих найденных украинских брендов именно амуниции.</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>Запросить. Цены 2021 года: поводок от 200 грн.</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>Сайт mrsnoopy.com не открывается — проверить, работает ли бренд.</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/mrsnoopythedog</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr"/>
-      <c r="W15" s="2" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mrsnoopythedog</t>
+        </is>
+      </c>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr">
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
         <is>
           <t>https://www.village.com.ua/village/city/animals/306957-dobirka-odyagu-dlya-tvarin</t>
         </is>
       </c>
-      <c r="AC15" s="2" t="inlineStr">
+      <c r="AF15" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2372,35 +2540,35 @@
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Данных не нашли.</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>Мастерская: ошейники из натуральной кожи под размер и цвет.</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Кожаная амуниция ручной работы.</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Неизвестно.</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>Контакты поиском не нашлись — искать в Instagram.</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr"/>
       <c r="W16" s="2" t="inlineStr"/>
@@ -2408,12 +2576,15 @@
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr">
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
         <is>
           <t>https://shotam.info/ukrains-ki-zootovary-top-10-vyrobnykiv-odiahu-budynochkiv-ta-smakolykiv-dlia-tvaryn/</t>
         </is>
       </c>
-      <c r="AC16" s="2" t="inlineStr">
+      <c r="AF16" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2463,56 +2634,59 @@
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Данных не нашли.</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>Адресники с гравировкой телефона владельца, разные формы и размеры.</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>Недорогое персональное дополнение к заказу.</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>На сайте одна строка: мастерская закрыта, ушли в ВСУ (проверено 12.10.2026).</t>
         </is>
       </c>
-      <c r="R17" s="3" t="inlineStr">
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>http://dogtag.kiev.ua</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr"/>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/dogtag.kiev.ua</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="2" t="inlineStr"/>
-      <c r="X17" s="2" t="inlineStr"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dogtag.kiev.ua</t>
+        </is>
+      </c>
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr">
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
         <is>
           <t>https://madeinua.org/catalog/tovary-dlia-tvaryn/dogtag/</t>
         </is>
       </c>
-      <c r="AC17" s="2" t="inlineStr">
+      <c r="AF17" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2562,64 +2736,67 @@
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Данных не нашли.</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>Сушёные говяжьи субпродукты широкой линейкой; производитель — ТД «Едельвейс Україна».</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>Работают оптом, большой ассортимент.</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>То же ограничение: ветеринарные разрешения на ввоз.</t>
         </is>
       </c>
-      <c r="R18" s="3" t="inlineStr">
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t>https://www.lasoshizsela.com/</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/lasochi_z_sela</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
+      <c r="X18" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/1171886699563323</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr"/>
-      <c r="W18" s="2" t="inlineStr"/>
-      <c r="X18" s="2" t="inlineStr"/>
       <c r="Y18" s="2" t="inlineStr"/>
-      <c r="Z18" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>korma.zp.ua@gmail.com</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr">
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
         <is>
           <t>https://www.lasoshizsela.com/</t>
         </is>
       </c>
-      <c r="AC18" s="2" t="inlineStr">
+      <c r="AF18" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2665,52 +2842,55 @@
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Данных не нашли.</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>Крафтовые сушёные лакомства из говядины.</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>Небольшое производство, без консервантов.</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>Запросить.</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>То же ограничение: ветеринарные разрешения на ввоз. 13.10.2026 сайт не работает: домен без содержимого.</t>
         </is>
       </c>
-      <c r="R19" s="3" t="inlineStr">
+      <c r="U19" s="3" t="inlineStr">
         <is>
           <t>https://snackon.com.ua/</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr"/>
-      <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr"/>
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="3" t="inlineStr">
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
         <is>
           <t>https://snackon.com.ua/</t>
         </is>
       </c>
-      <c r="AC19" s="2" t="inlineStr">
+      <c r="AF19" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2766,80 +2946,95 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>С оговорками</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Щенок дома</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Лежак и миски — недостающая часть набора «Щенок дома». Но бренд уже продаётся в ЕС, уникальности не даст.</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>Rozetka: 382 отзыва на 38 товаров из первой тысячи.</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>Лежак Dreamer Brown M — 2 289 грн (97 отзывов, 4,8 · Rozetka)
 Лежак Dreamer Velvet M — 3 290 грн (55 отзывов, 5,0 · Rozetka)
 Миски на подставке Lunch Bar S — 2 890 грн (21 отзыв, 4,9 · Rozetka)</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>Лежаки, диваны, миски на подставке, автогамаки; немного амуниции.</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>Известный бренд, но не наша стартовая категория.</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>Похоже, уже есть немецкий сайт — уникальности не будет.</t>
         </is>
       </c>
-      <c r="R20" s="3" t="inlineStr">
+      <c r="U20" s="3" t="inlineStr">
         <is>
           <t>https://harleyandcho.ua/</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="3" t="inlineStr">
         <is>
           <t>https://www.instagram.com/harleyandcho</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
+      <c r="X20" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/harleyandcho.main</t>
         </is>
       </c>
-      <c r="V20" s="3" t="inlineStr">
+      <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>https://www.etsy.com/listing/584236455</t>
         </is>
       </c>
-      <c r="W20" s="2" t="inlineStr"/>
-      <c r="X20" s="2" t="inlineStr"/>
-      <c r="Y20" s="3" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@HarleyandCho</t>
         </is>
       </c>
-      <c r="Z20" s="2" t="inlineStr">
+      <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>info@harleyandcho.ua</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
+      <c r="AD20" s="2" t="inlineStr">
         <is>
           <t>+380674527445</t>
         </is>
       </c>
-      <c r="AB20" s="3" t="inlineStr">
+      <c r="AE20" s="3" t="inlineStr">
         <is>
           <t>https://harleyandcho.ua/</t>
         </is>
       </c>
-      <c r="AC20" s="2" t="inlineStr">
+      <c r="AF20" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2848,7 +3043,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Collar / WAUDOG</t>
+          <t>Bronzedog</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2856,11 +3051,7 @@
           <t>Украина</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Чернигов</t>
-        </is>
-      </c>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Амуниция, Одежда</t>
@@ -2884,80 +3075,62 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Уже в ЕС</t>
+          <t>Не найдено</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>Rozetka: больше 7 000 отзывов по двум маркам; ниже — только товары для собак.</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Куртка AiryVest ONE — 969 грн (219 отзывов, 4,8 · Rozetka)
-Мячик Liker 7 — 95 грн (124 отзыва, 4,8 · Rozetka)
-Ошейник кожаный Waudog Classic — 224 грн (91 отзыв, 4,7 · Rozetka)
-Поводок Waudog Waterproof 3 м — 676 грн (75 отзывов, 4,8 · Rozetka)</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Ошейники, поводки, шлейки, адресники с QR, куртки AiryVest, Puller.</t>
-        </is>
-      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Ориентир по качеству, а не поставщик для уникального ассортимента.</t>
+          <t>Rozetka: 542 отзыва на 143 товара из первой тысячи.</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Опт в Польше — через COLLAR PL.</t>
+          <t>Адресник из нержавеющей стали «Косточка» — 129 грн (77 отзывов, 4,9 · Rozetka)
+Адресник с гравировкой «Косточка» 40×25 мм — 129 грн (53 отзыва, 5,0 · Rozetka)
+Поводок брезентовый светоотражающий 5 м — 392 грн (20 отзывов, 5,0 · Rozetka)</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Продаётся в 70 странах, в Польше есть своя компания.</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>https://collar.pl/</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/waudog.pl/</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/waudogpl</t>
-        </is>
-      </c>
+          <t>Ошейники, шлейки, поводки, намордники, одежда.</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Широкая линейка амуниции.</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Часть товара сделана в Китае — не «украинское производство».</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr"/>
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr"/>
       <c r="Y21" s="2" t="inlineStr"/>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t>info@waudog.pl</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>+48603742216</t>
-        </is>
-      </c>
-      <c r="AB21" s="3" t="inlineStr">
-        <is>
-          <t>https://forbes.ua/company/eksperimenty-na-zhivotnykh-17022021-1037</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>https://e-zoo.com.ua/ua/139-amuniciya-dlya-sobak/f/12956-biotan</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -2966,23 +3139,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Bronzedog</t>
+          <t>DIQPET</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Украина</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
+          <t>Китай</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Шанхай</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Амуниция, Одежда</t>
+          <t>Одежда</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Все размеры</t>
+          <t>Мелкие (до 8 кг)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2992,52 +3169,46 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Не начаты</t>
+          <t>В переписке</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Не найдено</t>
+          <t>Не применимо</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Rozetka: 542 отзыва на 143 товара из первой тысячи.</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Адресник из нержавеющей стали «Косточка» — 129 грн (77 отзывов, 4,9 · Rozetka)
-Адресник с гравировкой «Косточка» 40×25 мм — 129 грн (53 отзыва, 5,0 · Rozetka)
-Поводок брезентовый светоотражающий 5 м — 392 грн (20 отзывов, 5,0 · Rozetka)</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>Ошейники, шлейки, поводки, намордники, одежда.</t>
-        </is>
-      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Широкая линейка амуниции.</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Не проверяли.</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Часть товара сделана в Китае — не «украинское производство».</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr"/>
-      <c r="T22" s="2" t="inlineStr"/>
+          <t>Urban Trekking Onesie: комбинезон на четыре лапы со встроенными ботинками. Есть отдельная линия на собак до 40 кг.</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Функциональная вещь для грязи и мокрого снега; поставщик честно описывает ограничения ткани.</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>MOQ 30 шт., размеры можно смешивать, один цвет. Образцы: 2 шт. Прайс и доставка — в ответе от 07.10.2026.</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>Крой корейский: размеры меньше европейских, подбирать по обхвату груди. Ткань водоотталкивающая, не мембрана.</t>
+        </is>
+      </c>
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr"/>
@@ -3045,12 +3216,15 @@
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="3" t="inlineStr">
-        <is>
-          <t>https://e-zoo.com.ua/ua/139-amuniciya-dlya-sobak/f/12956-biotan</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr">
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>Ответ DIQPET на 11 вопросов, 07.10.2026 (файл у команды)</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
@@ -3059,19 +3233,15 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>DIQPET</t>
+          <t>Merlot Studio</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Шанхай</t>
-        </is>
-      </c>
+          <t>Корея</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Одежда</t>
@@ -3079,7 +3249,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Мелкие (до 8 кг)</t>
+          <t>Все размеры</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3100,35 +3270,35 @@
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Не проверяли.</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Urban Trekking Onesie: комбинезон на четыре лапы со встроенными ботинками. Есть отдельная линия на собак до 40 кг.</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>Функциональная вещь для грязи и мокрого снега; поставщик честно описывает ограничения ткани.</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>MOQ 30 шт., размеры можно смешивать, один цвет. Образцы: 2 шт. Прайс и доставка — в ответе от 07.10.2026.</t>
-        </is>
-      </c>
+      <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Крой корейский: размеры меньше европейских, подбирать по обхвату груди. Ткань водоотталкивающая, не мембрана.</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
-      <c r="T23" s="2" t="inlineStr"/>
+          <t>Одежда для собак: Coore Top / Suit, Ain Coat / Suit; размеры S–5XL, до 50 кг.</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Корейский ассортимент не только на мелких собак — редкость.</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>Каталог 25SS получен. MOQ и прайс дистрибьютора — запросить.</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>Контакт — в переписке у команды.</t>
+        </is>
+      </c>
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr"/>
       <c r="W23" s="2" t="inlineStr"/>
@@ -3136,193 +3306,105 @@
       <c r="Y23" s="2" t="inlineStr"/>
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="inlineStr"/>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>Ответ DIQPET на 11 вопросов, 07.10.2026 (файл у команды)</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr">
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>Каталог Merlot 25SS (файл у команды)</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
         <is>
           <t>13.10.2026</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Merlot Studio</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Корея</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Одежда</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Все размеры</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Без приоритета</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>В переписке</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Не проверяли.</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>Одежда для собак: Coore Top / Suit, Ain Coat / Suit; размеры S–5XL, до 50 кг.</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>Корейский ассортимент не только на мелких собак — редкость.</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>Каталог 25SS получен. MOQ и прайс дистрибьютора — запросить.</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>Контакт — в переписке у команды.</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr"/>
-      <c r="T24" s="2" t="inlineStr"/>
-      <c r="U24" s="2" t="inlineStr"/>
-      <c r="V24" s="2" t="inlineStr"/>
-      <c r="W24" s="2" t="inlineStr"/>
-      <c r="X24" s="2" t="inlineStr"/>
-      <c r="Y24" s="2" t="inlineStr"/>
-      <c r="Z24" s="2" t="inlineStr"/>
-      <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>Каталог Merlot 25SS (файл у команды)</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>13.10.2026</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AC24"/>
+  <autoFilter ref="A1:AF23"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB5" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB6" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB7" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T8" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y8" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB8" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y9" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X10" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB10" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T11" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y11" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB11" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB12" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T13" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y13" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB13" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB14" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB16" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T18" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T20" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V20" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y20" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T21" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y5" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE5" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE6" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE7" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z8" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB8" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE8" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z9" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA9" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE9" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA10" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE10" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X11" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB11" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE11" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE12" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X13" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB13" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE13" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE14" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE16" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X17" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE17" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X18" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE18" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE19" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X20" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y20" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE20" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE21" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3334,7 +3416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4628,7 +4710,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Collar / WAUDOG</t>
+          <t>Bronzedog</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4638,29 +4720,29 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Куртка AiryVest ONE</t>
+          <t>Адресник из нержавеющей стали «Косточка»</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>969 грн</t>
+          <t>129 грн</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>219 отзывов, 4,8 · Rozetka</t>
+          <t>77 отзывов, 4,9 · Rozetka</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>https://rozetka.com.ua/ua/422596260/p422596260/</t>
+          <t>https://rozetka.com.ua/ua/87752392/p87752392/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Collar / WAUDOG</t>
+          <t>Bronzedog</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4670,29 +4752,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Мячик Liker 7</t>
+          <t>Адресник с гравировкой «Косточка» 40×25 мм</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>95 грн</t>
+          <t>129 грн</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>124 отзыва, 4,8 · Rozetka</t>
+          <t>53 отзыва, 5,0 · Rozetka</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>https://rozetka.com.ua/ua/392251662/p392251662/</t>
+          <t>https://rozetka.com.ua/ua/87752506/p87752506/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Collar / WAUDOG</t>
+          <t>Bronzedog</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4702,155 +4784,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ошейник кожаный Waudog Classic</t>
+          <t>Поводок брезентовый светоотражающий 5 м</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>224 грн</t>
+          <t>392 грн</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>91 отзыв, 4,7 · Rozetka</t>
+          <t>20 отзывов, 5,0 · Rozetka</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>https://rozetka.com.ua/ua/569624830/p569624830/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Collar / WAUDOG</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Без приоритета</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Поводок Waudog Waterproof 3 м</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>676 грн</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>75 отзывов, 4,8 · Rozetka</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>https://rozetka.com.ua/ua/569423944/p569423944/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Bronzedog</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Без приоритета</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Адресник из нержавеющей стали «Косточка»</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>129 грн</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>77 отзывов, 4,9 · Rozetka</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>https://rozetka.com.ua/ua/87752392/p87752392/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Bronzedog</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Без приоритета</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Адресник с гравировкой «Косточка» 40×25 мм</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>129 грн</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>53 отзыва, 5,0 · Rozetka</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>https://rozetka.com.ua/ua/87752506/p87752506/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Bronzedog</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Без приоритета</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Поводок брезентовый светоотражающий 5 м</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>392 грн</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>20 отзывов, 5,0 · Rozetka</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
           <t>https://rozetka.com.ua/ua/305319368/p305319368/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F47"/>
+  <autoFilter ref="A1:F43"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -4894,10 +4848,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
